--- a/quickbook_summary.xlsx
+++ b/quickbook_summary.xlsx
@@ -2276,7 +2276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1265"/>
+  <dimension ref="A1:H1346"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -41989,30 +41989,22 @@
       </c>
       <c r="B1122" s="3" t="inlineStr">
         <is>
-          <t>5121 · Freight &amp; Shipping (Direct)</t>
+          <t>5115 · Rent - Equipment (direct)</t>
         </is>
       </c>
       <c r="C1122" s="5" t="n">
-        <v>150</v>
+        <v>3.51</v>
       </c>
       <c r="D1122" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
-        </is>
-      </c>
-      <c r="E1122" s="3" t="inlineStr">
-        <is>
-          <t>93745414-2</t>
-        </is>
-      </c>
-      <c r="F1122" s="3" t="inlineStr">
-        <is>
-          <t>Shipping</t>
-        </is>
-      </c>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="E1122" s="3" t="inlineStr"/>
+      <c r="F1122" s="3" t="inlineStr"/>
       <c r="G1122" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>2313. · Chase Mileage Plus CW (5726)</t>
         </is>
       </c>
       <c r="H1122" s="4" t="n">
@@ -42021,30 +42013,34 @@
     </row>
     <row r="1123">
       <c r="A1123" s="2" t="n">
-        <v>45997</v>
+        <v>45996</v>
       </c>
       <c r="B1123" s="3" t="inlineStr">
         <is>
-          <t>5123 · Auto fuel (Direct)</t>
+          <t>5121 · Freight &amp; Shipping (Direct)</t>
         </is>
       </c>
       <c r="C1123" s="5" t="n">
-        <v>38.28</v>
+        <v>150</v>
       </c>
       <c r="D1123" s="3" t="inlineStr">
         <is>
-          <t>Credit Card Charge</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E1123" s="3" t="inlineStr">
         <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="F1123" s="3" t="inlineStr"/>
+          <t>93745414-2</t>
+        </is>
+      </c>
+      <c r="F1123" s="3" t="inlineStr">
+        <is>
+          <t>Shipping</t>
+        </is>
+      </c>
       <c r="G1123" s="3" t="inlineStr">
         <is>
-          <t>2323 · Shell Credit Card - WEX</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="H1123" s="4" t="n">
@@ -42053,34 +42049,30 @@
     </row>
     <row r="1124">
       <c r="A1124" s="2" t="n">
-        <v>45999</v>
+        <v>45997</v>
       </c>
       <c r="B1124" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5123 · Auto fuel (Direct)</t>
         </is>
       </c>
       <c r="C1124" s="5" t="n">
-        <v>165</v>
+        <v>38.28</v>
       </c>
       <c r="D1124" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>Credit Card Charge</t>
         </is>
       </c>
       <c r="E1124" s="3" t="inlineStr">
         <is>
-          <t>18693174</t>
-        </is>
-      </c>
-      <c r="F1124" s="3" t="inlineStr">
-        <is>
-          <t>THMWK-20-1U-G-1 / TE Wire &amp; Cable Type K thermocouple</t>
-        </is>
-      </c>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="F1124" s="3" t="inlineStr"/>
       <c r="G1124" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>2323 · Shell Credit Card - WEX</t>
         </is>
       </c>
       <c r="H1124" s="4" t="n">
@@ -42097,7 +42089,7 @@
         </is>
       </c>
       <c r="C1125" s="5" t="n">
-        <v>80</v>
+        <v>165</v>
       </c>
       <c r="D1125" s="3" t="inlineStr">
         <is>
@@ -42111,7 +42103,7 @@
       </c>
       <c r="F1125" s="3" t="inlineStr">
         <is>
-          <t>THMK-MP - ProSense Type K thermocouple</t>
+          <t>THMWK-20-1U-G-1 / TE Wire &amp; Cable Type K thermocouple</t>
         </is>
       </c>
       <c r="G1125" s="3" t="inlineStr">
@@ -42133,7 +42125,7 @@
         </is>
       </c>
       <c r="C1126" s="5" t="n">
-        <v>16.54</v>
+        <v>80</v>
       </c>
       <c r="D1126" s="3" t="inlineStr">
         <is>
@@ -42147,7 +42139,7 @@
       </c>
       <c r="F1126" s="3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>THMK-MP - ProSense Type K thermocouple</t>
         </is>
       </c>
       <c r="G1126" s="3" t="inlineStr">
@@ -42165,11 +42157,11 @@
       </c>
       <c r="B1127" s="3" t="inlineStr">
         <is>
-          <t>5121 · Freight &amp; Shipping (Direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C1127" s="5" t="n">
-        <v>1750</v>
+        <v>16.54</v>
       </c>
       <c r="D1127" s="3" t="inlineStr">
         <is>
@@ -42178,12 +42170,12 @@
       </c>
       <c r="E1127" s="3" t="inlineStr">
         <is>
-          <t>3043039</t>
+          <t>18693174</t>
         </is>
       </c>
       <c r="F1127" s="3" t="inlineStr">
         <is>
-          <t>CInc to Ma</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="G1127" s="3" t="inlineStr">
@@ -42201,26 +42193,30 @@
       </c>
       <c r="B1128" s="3" t="inlineStr">
         <is>
-          <t>5123 · Auto fuel (Direct)</t>
+          <t>5121 · Freight &amp; Shipping (Direct)</t>
         </is>
       </c>
       <c r="C1128" s="5" t="n">
-        <v>67.54000000000001</v>
+        <v>1750</v>
       </c>
       <c r="D1128" s="3" t="inlineStr">
         <is>
-          <t>Credit Card Charge</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E1128" s="3" t="inlineStr">
         <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="F1128" s="3" t="inlineStr"/>
+          <t>3043039</t>
+        </is>
+      </c>
+      <c r="F1128" s="3" t="inlineStr">
+        <is>
+          <t>CInc to Ma</t>
+        </is>
+      </c>
       <c r="G1128" s="3" t="inlineStr">
         <is>
-          <t>2323 · Shell Credit Card - WEX</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="H1128" s="4" t="n">
@@ -42229,34 +42225,30 @@
     </row>
     <row r="1129">
       <c r="A1129" s="2" t="n">
-        <v>46000</v>
+        <v>45999</v>
       </c>
       <c r="B1129" s="3" t="inlineStr">
         <is>
-          <t>5107 · Travel - Other (Direct)</t>
+          <t>5123 · Auto fuel (Direct)</t>
         </is>
       </c>
       <c r="C1129" s="5" t="n">
-        <v>140</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="D1129" s="3" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Credit Card Charge</t>
         </is>
       </c>
       <c r="E1129" s="3" t="inlineStr">
         <is>
-          <t>ER</t>
-        </is>
-      </c>
-      <c r="F1129" s="3" t="inlineStr">
-        <is>
-          <t>overweight bag</t>
-        </is>
-      </c>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="F1129" s="3" t="inlineStr"/>
       <c r="G1129" s="3" t="inlineStr">
         <is>
-          <t>1006.1 · (NEW) Calif B &amp; T Checking</t>
+          <t>2323 · Shell Credit Card - WEX</t>
         </is>
       </c>
       <c r="H1129" s="4" t="n">
@@ -42269,30 +42261,30 @@
       </c>
       <c r="B1130" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5107 · Travel - Other (Direct)</t>
         </is>
       </c>
       <c r="C1130" s="5" t="n">
-        <v>165.8</v>
+        <v>140</v>
       </c>
       <c r="D1130" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="E1130" s="3" t="inlineStr">
         <is>
-          <t>93763536</t>
+          <t>ER</t>
         </is>
       </c>
       <c r="F1130" s="3" t="inlineStr">
         <is>
-          <t>|CONC RED 8x6" CS STD A234WPB</t>
+          <t>overweight bag</t>
         </is>
       </c>
       <c r="G1130" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>1006.1 · (NEW) Calif B &amp; T Checking</t>
         </is>
       </c>
       <c r="H1130" s="4" t="n">
@@ -42309,7 +42301,7 @@
         </is>
       </c>
       <c r="C1131" s="5" t="n">
-        <v>267.6</v>
+        <v>165.8</v>
       </c>
       <c r="D1131" s="3" t="inlineStr">
         <is>
@@ -42323,7 +42315,7 @@
       </c>
       <c r="F1131" s="3" t="inlineStr">
         <is>
-          <t>|FLG SO RF 6" CS 150 IMP A105</t>
+          <t>|CONC RED 8x6" CS STD A234WPB</t>
         </is>
       </c>
       <c r="G1131" s="3" t="inlineStr">
@@ -42345,7 +42337,7 @@
         </is>
       </c>
       <c r="C1132" s="5" t="n">
-        <v>95.18000000000001</v>
+        <v>267.6</v>
       </c>
       <c r="D1132" s="3" t="inlineStr">
         <is>
@@ -42359,7 +42351,7 @@
       </c>
       <c r="F1132" s="3" t="inlineStr">
         <is>
-          <t>|CONC RED 8x4" CS STD A234WPB</t>
+          <t>|FLG SO RF 6" CS 150 IMP A105</t>
         </is>
       </c>
       <c r="G1132" s="3" t="inlineStr">
@@ -42381,7 +42373,7 @@
         </is>
       </c>
       <c r="C1133" s="5" t="n">
-        <v>190.08</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="D1133" s="3" t="inlineStr">
         <is>
@@ -42395,7 +42387,7 @@
       </c>
       <c r="F1133" s="3" t="inlineStr">
         <is>
-          <t>|CONC RED 6x4" CS STD A234WPB</t>
+          <t>|CONC RED 8x4" CS STD A234WPB</t>
         </is>
       </c>
       <c r="G1133" s="3" t="inlineStr">
@@ -42417,7 +42409,7 @@
         </is>
       </c>
       <c r="C1134" s="5" t="n">
-        <v>289.08</v>
+        <v>190.08</v>
       </c>
       <c r="D1134" s="3" t="inlineStr">
         <is>
@@ -42431,7 +42423,7 @@
       </c>
       <c r="F1134" s="3" t="inlineStr">
         <is>
-          <t>|ELL 90DEG LR 8" CS STD IMP A</t>
+          <t>|CONC RED 6x4" CS STD A234WPB</t>
         </is>
       </c>
       <c r="G1134" s="3" t="inlineStr">
@@ -42453,7 +42445,7 @@
         </is>
       </c>
       <c r="C1135" s="5" t="n">
-        <v>55.43</v>
+        <v>289.08</v>
       </c>
       <c r="D1135" s="3" t="inlineStr">
         <is>
@@ -42467,7 +42459,7 @@
       </c>
       <c r="F1135" s="3" t="inlineStr">
         <is>
-          <t>tax</t>
+          <t>|ELL 90DEG LR 8" CS STD IMP A</t>
         </is>
       </c>
       <c r="G1135" s="3" t="inlineStr">
@@ -42489,7 +42481,7 @@
         </is>
       </c>
       <c r="C1136" s="5" t="n">
-        <v>210</v>
+        <v>55.43</v>
       </c>
       <c r="D1136" s="3" t="inlineStr">
         <is>
@@ -42498,12 +42490,12 @@
       </c>
       <c r="E1136" s="3" t="inlineStr">
         <is>
-          <t>93745414</t>
+          <t>93763536</t>
         </is>
       </c>
       <c r="F1136" s="3" t="inlineStr">
         <is>
-          <t>|BOLTPAK 4" RING 150 1/8" NAS</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="G1136" s="3" t="inlineStr">
@@ -42525,7 +42517,7 @@
         </is>
       </c>
       <c r="C1137" s="5" t="n">
-        <v>330.84</v>
+        <v>210</v>
       </c>
       <c r="D1137" s="3" t="inlineStr">
         <is>
@@ -42539,7 +42531,7 @@
       </c>
       <c r="F1137" s="3" t="inlineStr">
         <is>
-          <t>|BOLTPAK 5" RING 150 1/8" NAS</t>
+          <t>|BOLTPAK 4" RING 150 1/8" NAS</t>
         </is>
       </c>
       <c r="G1137" s="3" t="inlineStr">
@@ -42561,7 +42553,7 @@
         </is>
       </c>
       <c r="C1138" s="5" t="n">
-        <v>138.1</v>
+        <v>330.84</v>
       </c>
       <c r="D1138" s="3" t="inlineStr">
         <is>
@@ -42575,7 +42567,7 @@
       </c>
       <c r="F1138" s="3" t="inlineStr">
         <is>
-          <t>|BOLTPAK 6" RING 150 1/8" NAS</t>
+          <t>|BOLTPAK 5" RING 150 1/8" NAS</t>
         </is>
       </c>
       <c r="G1138" s="3" t="inlineStr">
@@ -42597,7 +42589,7 @@
         </is>
       </c>
       <c r="C1139" s="5" t="n">
-        <v>386.68</v>
+        <v>138.1</v>
       </c>
       <c r="D1139" s="3" t="inlineStr">
         <is>
@@ -42606,7 +42598,7 @@
       </c>
       <c r="E1139" s="3" t="inlineStr">
         <is>
-          <t>|BOLTPAK 6" RING 150</t>
+          <t>93745414</t>
         </is>
       </c>
       <c r="F1139" s="3" t="inlineStr">
@@ -42633,7 +42625,7 @@
         </is>
       </c>
       <c r="C1140" s="5" t="n">
-        <v>105</v>
+        <v>386.68</v>
       </c>
       <c r="D1140" s="3" t="inlineStr">
         <is>
@@ -42669,7 +42661,7 @@
         </is>
       </c>
       <c r="C1141" s="5" t="n">
-        <v>27.04</v>
+        <v>105</v>
       </c>
       <c r="D1141" s="3" t="inlineStr">
         <is>
@@ -42683,7 +42675,7 @@
       </c>
       <c r="F1141" s="3" t="inlineStr">
         <is>
-          <t>tax</t>
+          <t>|BOLTPAK 6" RING 150 1/8" NAS</t>
         </is>
       </c>
       <c r="G1141" s="3" t="inlineStr">
@@ -42705,7 +42697,7 @@
         </is>
       </c>
       <c r="C1142" s="5" t="n">
-        <v>27.24</v>
+        <v>27.04</v>
       </c>
       <c r="D1142" s="3" t="inlineStr">
         <is>
@@ -42714,12 +42706,12 @@
       </c>
       <c r="E1142" s="3" t="inlineStr">
         <is>
-          <t>56595839</t>
+          <t>|BOLTPAK 6" RING 150</t>
         </is>
       </c>
       <c r="F1142" s="3" t="inlineStr">
         <is>
-          <t>Uncoated Carbon Steel Pipe and Conduit Tap, 1/4 NPT</t>
+          <t>tax</t>
         </is>
       </c>
       <c r="G1142" s="3" t="inlineStr">
@@ -42741,7 +42733,7 @@
         </is>
       </c>
       <c r="C1143" s="5" t="n">
-        <v>33.54</v>
+        <v>27.24</v>
       </c>
       <c r="D1143" s="3" t="inlineStr">
         <is>
@@ -42755,7 +42747,7 @@
       </c>
       <c r="F1143" s="3" t="inlineStr">
         <is>
-          <t>Maintenance-Length High-Speed Steel Drill Bit, Black-and-Gold-Oxide Finish, 7/16" Size</t>
+          <t>Uncoated Carbon Steel Pipe and Conduit Tap, 1/4 NPT</t>
         </is>
       </c>
       <c r="G1143" s="3" t="inlineStr">
@@ -42777,7 +42769,7 @@
         </is>
       </c>
       <c r="C1144" s="5" t="n">
-        <v>21.59</v>
+        <v>33.54</v>
       </c>
       <c r="D1144" s="3" t="inlineStr">
         <is>
@@ -42791,7 +42783,7 @@
       </c>
       <c r="F1144" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Brass Barbed Hose Fitting for Air and Water, Straight Adapter for 3/16" Hose ID, 1/4 NPTF Male,...</t>
+          <t>Maintenance-Length High-Speed Steel Drill Bit, Black-and-Gold-Oxide Finish, 7/16" Size</t>
         </is>
       </c>
       <c r="G1144" s="3" t="inlineStr">
@@ -42813,7 +42805,7 @@
         </is>
       </c>
       <c r="C1145" s="5" t="n">
-        <v>6.51</v>
+        <v>21.59</v>
       </c>
       <c r="D1145" s="3" t="inlineStr">
         <is>
@@ -42827,7 +42819,7 @@
       </c>
       <c r="F1145" s="3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t xml:space="preserve">	Brass Barbed Hose Fitting for Air and Water, Straight Adapter for 3/16" Hose ID, 1/4 NPTF Male,...</t>
         </is>
       </c>
       <c r="G1145" s="3" t="inlineStr">
@@ -42849,7 +42841,7 @@
         </is>
       </c>
       <c r="C1146" s="5" t="n">
-        <v>68.76000000000001</v>
+        <v>6.51</v>
       </c>
       <c r="D1146" s="3" t="inlineStr">
         <is>
@@ -42858,12 +42850,12 @@
       </c>
       <c r="E1146" s="3" t="inlineStr">
         <is>
-          <t>56655575</t>
+          <t>56595839</t>
         </is>
       </c>
       <c r="F1146" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">	Ridgid No. E-1032S Cutter Wheel for Ridgid Electric Pipe Threader</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="G1146" s="3" t="inlineStr">
@@ -42885,7 +42877,7 @@
         </is>
       </c>
       <c r="C1147" s="5" t="n">
-        <v>5.52</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="D1147" s="3" t="inlineStr">
         <is>
@@ -42899,7 +42891,7 @@
       </c>
       <c r="F1147" s="3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t xml:space="preserve">	Ridgid No. E-1032S Cutter Wheel for Ridgid Electric Pipe Threader</t>
         </is>
       </c>
       <c r="G1147" s="3" t="inlineStr">
@@ -42917,11 +42909,11 @@
       </c>
       <c r="B1148" s="3" t="inlineStr">
         <is>
-          <t>5115 · Rent - Equipment (direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C1148" s="5" t="n">
-        <v>2166</v>
+        <v>5.52</v>
       </c>
       <c r="D1148" s="3" t="inlineStr">
         <is>
@@ -42930,12 +42922,12 @@
       </c>
       <c r="E1148" s="3" t="inlineStr">
         <is>
-          <t>254738310-002</t>
+          <t>56655575</t>
         </is>
       </c>
       <c r="F1148" s="3" t="inlineStr">
         <is>
-          <t>SKID STEER TRACK LOADER 1700-1999#</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="G1148" s="3" t="inlineStr">
@@ -42957,7 +42949,7 @@
         </is>
       </c>
       <c r="C1149" s="5" t="n">
-        <v>43.32</v>
+        <v>2166</v>
       </c>
       <c r="D1149" s="3" t="inlineStr">
         <is>
@@ -42971,7 +42963,7 @@
       </c>
       <c r="F1149" s="3" t="inlineStr">
         <is>
-          <t>Environmental Charge</t>
+          <t>SKID STEER TRACK LOADER 1700-1999#</t>
         </is>
       </c>
       <c r="G1149" s="3" t="inlineStr">
@@ -42993,7 +42985,7 @@
         </is>
       </c>
       <c r="C1150" s="5" t="n">
-        <v>172.33</v>
+        <v>43.32</v>
       </c>
       <c r="D1150" s="3" t="inlineStr">
         <is>
@@ -43007,7 +42999,7 @@
       </c>
       <c r="F1150" s="3" t="inlineStr">
         <is>
-          <t>Taxes &amp; Fees</t>
+          <t>Environmental Charge</t>
         </is>
       </c>
       <c r="G1150" s="3" t="inlineStr">
@@ -43029,7 +43021,7 @@
         </is>
       </c>
       <c r="C1151" s="5" t="n">
-        <v>561</v>
+        <v>172.33</v>
       </c>
       <c r="D1151" s="3" t="inlineStr">
         <is>
@@ -43038,12 +43030,12 @@
       </c>
       <c r="E1151" s="3" t="inlineStr">
         <is>
-          <t>256400488-001</t>
+          <t>254738310-002</t>
         </is>
       </c>
       <c r="F1151" s="3" t="inlineStr">
         <is>
-          <t>PV2412532S OFFICE TRAILER 8X24</t>
+          <t>Taxes &amp; Fees</t>
         </is>
       </c>
       <c r="G1151" s="3" t="inlineStr">
@@ -43065,7 +43057,7 @@
         </is>
       </c>
       <c r="C1152" s="5" t="n">
-        <v>66.5</v>
+        <v>561</v>
       </c>
       <c r="D1152" s="3" t="inlineStr">
         <is>
@@ -43079,7 +43071,7 @@
       </c>
       <c r="F1152" s="3" t="inlineStr">
         <is>
-          <t>OFFICE TRAILER STEPS</t>
+          <t>PV2412532S OFFICE TRAILER 8X24</t>
         </is>
       </c>
       <c r="G1152" s="3" t="inlineStr">
@@ -43101,7 +43093,7 @@
         </is>
       </c>
       <c r="C1153" s="5" t="n">
-        <v>570</v>
+        <v>66.5</v>
       </c>
       <c r="D1153" s="3" t="inlineStr">
         <is>
@@ -43115,7 +43107,7 @@
       </c>
       <c r="F1153" s="3" t="inlineStr">
         <is>
-          <t>BLOCK AND LEVEL + INSTALL OF 4 ANCHORS</t>
+          <t>OFFICE TRAILER STEPS</t>
         </is>
       </c>
       <c r="G1153" s="3" t="inlineStr">
@@ -43137,7 +43129,7 @@
         </is>
       </c>
       <c r="C1154" s="5" t="n">
-        <v>710</v>
+        <v>570</v>
       </c>
       <c r="D1154" s="3" t="inlineStr">
         <is>
@@ -43151,7 +43143,7 @@
       </c>
       <c r="F1154" s="3" t="inlineStr">
         <is>
-          <t>Delivery &amp; PIck Up Charge</t>
+          <t>BLOCK AND LEVEL + INSTALL OF 4 ANCHORS</t>
         </is>
       </c>
       <c r="G1154" s="3" t="inlineStr">
@@ -43173,7 +43165,7 @@
         </is>
       </c>
       <c r="C1155" s="5" t="n">
-        <v>375</v>
+        <v>710</v>
       </c>
       <c r="D1155" s="3" t="inlineStr">
         <is>
@@ -43187,7 +43179,7 @@
       </c>
       <c r="F1155" s="3" t="inlineStr">
         <is>
-          <t>Tear Down</t>
+          <t>Delivery &amp; PIck Up Charge</t>
         </is>
       </c>
       <c r="G1155" s="3" t="inlineStr">
@@ -43209,7 +43201,7 @@
         </is>
       </c>
       <c r="C1156" s="5" t="n">
-        <v>168.12</v>
+        <v>375</v>
       </c>
       <c r="D1156" s="3" t="inlineStr">
         <is>
@@ -43223,7 +43215,7 @@
       </c>
       <c r="F1156" s="3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Tear Down</t>
         </is>
       </c>
       <c r="G1156" s="3" t="inlineStr">
@@ -43241,11 +43233,11 @@
       </c>
       <c r="B1157" s="3" t="inlineStr">
         <is>
-          <t>5121 · Freight &amp; Shipping (Direct)</t>
+          <t>5115 · Rent - Equipment (direct)</t>
         </is>
       </c>
       <c r="C1157" s="5" t="n">
-        <v>437.05</v>
+        <v>168.12</v>
       </c>
       <c r="D1157" s="3" t="inlineStr">
         <is>
@@ -43254,12 +43246,12 @@
       </c>
       <c r="E1157" s="3" t="inlineStr">
         <is>
-          <t>93745414</t>
+          <t>256400488-001</t>
         </is>
       </c>
       <c r="F1157" s="3" t="inlineStr">
         <is>
-          <t>Shippng &amp; Handling</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="G1157" s="3" t="inlineStr">
@@ -43281,7 +43273,7 @@
         </is>
       </c>
       <c r="C1158" s="5" t="n">
-        <v>10.68</v>
+        <v>437.05</v>
       </c>
       <c r="D1158" s="3" t="inlineStr">
         <is>
@@ -43290,12 +43282,12 @@
       </c>
       <c r="E1158" s="3" t="inlineStr">
         <is>
-          <t>56595839</t>
+          <t>93745414</t>
         </is>
       </c>
       <c r="F1158" s="3" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Shippng &amp; Handling</t>
         </is>
       </c>
       <c r="G1158" s="3" t="inlineStr">
@@ -43317,7 +43309,7 @@
         </is>
       </c>
       <c r="C1159" s="5" t="n">
-        <v>10.15</v>
+        <v>10.68</v>
       </c>
       <c r="D1159" s="3" t="inlineStr">
         <is>
@@ -43326,7 +43318,7 @@
       </c>
       <c r="E1159" s="3" t="inlineStr">
         <is>
-          <t>56655575</t>
+          <t>56595839</t>
         </is>
       </c>
       <c r="F1159" s="3" t="inlineStr">
@@ -43345,15 +43337,15 @@
     </row>
     <row r="1160">
       <c r="A1160" s="2" t="n">
-        <v>46001</v>
+        <v>46000</v>
       </c>
       <c r="B1160" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5121 · Freight &amp; Shipping (Direct)</t>
         </is>
       </c>
       <c r="C1160" s="5" t="n">
-        <v>45.3</v>
+        <v>10.15</v>
       </c>
       <c r="D1160" s="3" t="inlineStr">
         <is>
@@ -43362,12 +43354,12 @@
       </c>
       <c r="E1160" s="3" t="inlineStr">
         <is>
-          <t>9737553678</t>
+          <t>56655575</t>
         </is>
       </c>
       <c r="F1160" s="3" t="inlineStr">
         <is>
-          <t>CUTTING OIL,1 GAL,CAN</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="G1160" s="3" t="inlineStr">
@@ -43389,7 +43381,7 @@
         </is>
       </c>
       <c r="C1161" s="5" t="n">
-        <v>3.53</v>
+        <v>45.3</v>
       </c>
       <c r="D1161" s="3" t="inlineStr">
         <is>
@@ -43403,7 +43395,7 @@
       </c>
       <c r="F1161" s="3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>CUTTING OIL,1 GAL,CAN</t>
         </is>
       </c>
       <c r="G1161" s="3" t="inlineStr">
@@ -43425,7 +43417,7 @@
         </is>
       </c>
       <c r="C1162" s="5" t="n">
-        <v>54.77</v>
+        <v>3.53</v>
       </c>
       <c r="D1162" s="3" t="inlineStr">
         <is>
@@ -43434,12 +43426,12 @@
       </c>
       <c r="E1162" s="3" t="inlineStr">
         <is>
-          <t>9737553660</t>
+          <t>9737553678</t>
         </is>
       </c>
       <c r="F1162" s="3" t="inlineStr">
         <is>
-          <t>THROWOUT LEVER</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="G1162" s="3" t="inlineStr">
@@ -43461,7 +43453,7 @@
         </is>
       </c>
       <c r="C1163" s="5" t="n">
-        <v>140.7</v>
+        <v>54.77</v>
       </c>
       <c r="D1163" s="3" t="inlineStr">
         <is>
@@ -43475,7 +43467,7 @@
       </c>
       <c r="F1163" s="3" t="inlineStr">
         <is>
-          <t>CARRIAGE FEED LEVER</t>
+          <t>THROWOUT LEVER</t>
         </is>
       </c>
       <c r="G1163" s="3" t="inlineStr">
@@ -43497,7 +43489,7 @@
         </is>
       </c>
       <c r="C1164" s="5" t="n">
-        <v>15.25</v>
+        <v>140.7</v>
       </c>
       <c r="D1164" s="3" t="inlineStr">
         <is>
@@ -43511,7 +43503,7 @@
       </c>
       <c r="F1164" s="3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>CARRIAGE FEED LEVER</t>
         </is>
       </c>
       <c r="G1164" s="3" t="inlineStr">
@@ -43525,30 +43517,34 @@
     </row>
     <row r="1165">
       <c r="A1165" s="2" t="n">
-        <v>46002</v>
+        <v>46001</v>
       </c>
       <c r="B1165" s="3" t="inlineStr">
         <is>
-          <t>5123 · Auto fuel (Direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C1165" s="5" t="n">
-        <v>29.02</v>
+        <v>15.25</v>
       </c>
       <c r="D1165" s="3" t="inlineStr">
         <is>
-          <t>Credit Card Charge</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E1165" s="3" t="inlineStr">
         <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="F1165" s="3" t="inlineStr"/>
+          <t>9737553660</t>
+        </is>
+      </c>
+      <c r="F1165" s="3" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
       <c r="G1165" s="3" t="inlineStr">
         <is>
-          <t>2323 · Shell Credit Card - WEX</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="H1165" s="4" t="n">
@@ -43565,7 +43561,7 @@
         </is>
       </c>
       <c r="C1166" s="5" t="n">
-        <v>67.87</v>
+        <v>29.02</v>
       </c>
       <c r="D1166" s="3" t="inlineStr">
         <is>
@@ -43589,34 +43585,30 @@
     </row>
     <row r="1167">
       <c r="A1167" s="2" t="n">
-        <v>46003</v>
+        <v>46002</v>
       </c>
       <c r="B1167" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5123 · Auto fuel (Direct)</t>
         </is>
       </c>
       <c r="C1167" s="5" t="n">
-        <v>350</v>
+        <v>67.87</v>
       </c>
       <c r="D1167" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
+          <t>Credit Card Charge</t>
         </is>
       </c>
       <c r="E1167" s="3" t="inlineStr">
         <is>
-          <t>16798</t>
-        </is>
-      </c>
-      <c r="F1167" s="3" t="inlineStr">
-        <is>
-          <t>Andy Remillard Per diem for week of 12/15/2025 - 12/21/2025</t>
-        </is>
-      </c>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="F1167" s="3" t="inlineStr"/>
       <c r="G1167" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2323 · Shell Credit Card - WEX</t>
         </is>
       </c>
       <c r="H1167" s="4" t="n">
@@ -43633,7 +43625,7 @@
         </is>
       </c>
       <c r="C1168" s="5" t="n">
-        <v>650</v>
+        <v>350</v>
       </c>
       <c r="D1168" s="3" t="inlineStr">
         <is>
@@ -43647,7 +43639,7 @@
       </c>
       <c r="F1168" s="3" t="inlineStr">
         <is>
-          <t>Brian Krumbholz Per diem for week of 12/7/2025 - 12/21/2025</t>
+          <t>Andy Remillard Per diem for week of 12/15/2025 - 12/21/2025</t>
         </is>
       </c>
       <c r="G1168" s="3" t="inlineStr">
@@ -43669,7 +43661,7 @@
         </is>
       </c>
       <c r="C1169" s="5" t="n">
-        <v>350</v>
+        <v>650</v>
       </c>
       <c r="D1169" s="3" t="inlineStr">
         <is>
@@ -43683,7 +43675,7 @@
       </c>
       <c r="F1169" s="3" t="inlineStr">
         <is>
-          <t>Levi Winslow Per diem for week of 12/15/2025 - 12/21/2025</t>
+          <t>Brian Krumbholz Per diem for week of 12/7/2025 - 12/21/2025</t>
         </is>
       </c>
       <c r="G1169" s="3" t="inlineStr">
@@ -43719,7 +43711,7 @@
       </c>
       <c r="F1170" s="3" t="inlineStr">
         <is>
-          <t>Luke Giguere Per diem for week of 12/15/2025 - 12/21/2025</t>
+          <t>Levi Winslow Per diem for week of 12/15/2025 - 12/21/2025</t>
         </is>
       </c>
       <c r="G1170" s="3" t="inlineStr">
@@ -43755,7 +43747,7 @@
       </c>
       <c r="F1171" s="3" t="inlineStr">
         <is>
-          <t>Mike Cogswell Per diem for week of 12/15/2025 - 12/21/2025</t>
+          <t>Luke Giguere Per diem for week of 12/15/2025 - 12/21/2025</t>
         </is>
       </c>
       <c r="G1171" s="3" t="inlineStr">
@@ -43777,7 +43769,7 @@
         </is>
       </c>
       <c r="C1172" s="5" t="n">
-        <v>750</v>
+        <v>350</v>
       </c>
       <c r="D1172" s="3" t="inlineStr">
         <is>
@@ -43791,7 +43783,7 @@
       </c>
       <c r="F1172" s="3" t="inlineStr">
         <is>
-          <t>Ryan Ordelt Per diem for week of 12/15/2025 - 12/21/2025</t>
+          <t>Mike Cogswell Per diem for week of 12/15/2025 - 12/21/2025</t>
         </is>
       </c>
       <c r="G1172" s="3" t="inlineStr">
@@ -43813,7 +43805,7 @@
         </is>
       </c>
       <c r="C1173" s="5" t="n">
-        <v>100</v>
+        <v>750</v>
       </c>
       <c r="D1173" s="3" t="inlineStr">
         <is>
@@ -43827,7 +43819,7 @@
       </c>
       <c r="F1173" s="3" t="inlineStr">
         <is>
-          <t>Ryan Ordelt Per diem credit for 11/22/25 - 11/23/25</t>
+          <t>Ryan Ordelt Per diem for week of 12/15/2025 - 12/21/2025</t>
         </is>
       </c>
       <c r="G1173" s="3" t="inlineStr">
@@ -43849,7 +43841,7 @@
         </is>
       </c>
       <c r="C1174" s="5" t="n">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="D1174" s="3" t="inlineStr">
         <is>
@@ -43863,7 +43855,7 @@
       </c>
       <c r="F1174" s="3" t="inlineStr">
         <is>
-          <t>Tony Madrid Per diem for week of 12/15/2025 - 12/21/2025</t>
+          <t>Ryan Ordelt Per diem credit for 11/22/25 - 11/23/25</t>
         </is>
       </c>
       <c r="G1174" s="3" t="inlineStr">
@@ -43881,30 +43873,30 @@
       </c>
       <c r="B1175" s="3" t="inlineStr">
         <is>
-          <t>5121 · Freight &amp; Shipping (Direct)</t>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
         </is>
       </c>
       <c r="C1175" s="5" t="n">
-        <v>493.87</v>
+        <v>350</v>
       </c>
       <c r="D1175" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>General Journal</t>
         </is>
       </c>
       <c r="E1175" s="3" t="inlineStr">
         <is>
-          <t>6235199863</t>
+          <t>16798</t>
         </is>
       </c>
       <c r="F1175" s="3" t="inlineStr">
         <is>
-          <t>Maine to OH</t>
+          <t>Tony Madrid Per diem for week of 12/15/2025 - 12/21/2025</t>
         </is>
       </c>
       <c r="G1175" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
         </is>
       </c>
       <c r="H1175" s="4" t="n">
@@ -43917,26 +43909,30 @@
       </c>
       <c r="B1176" s="3" t="inlineStr">
         <is>
-          <t>5123 · Auto fuel (Direct)</t>
+          <t>5121 · Freight &amp; Shipping (Direct)</t>
         </is>
       </c>
       <c r="C1176" s="5" t="n">
-        <v>44.35</v>
+        <v>493.87</v>
       </c>
       <c r="D1176" s="3" t="inlineStr">
         <is>
-          <t>Credit Card Charge</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E1176" s="3" t="inlineStr">
         <is>
-          <t>AR</t>
-        </is>
-      </c>
-      <c r="F1176" s="3" t="inlineStr"/>
+          <t>6235199863</t>
+        </is>
+      </c>
+      <c r="F1176" s="3" t="inlineStr">
+        <is>
+          <t>Maine to OH</t>
+        </is>
+      </c>
       <c r="G1176" s="3" t="inlineStr">
         <is>
-          <t>2323 · Shell Credit Card - WEX</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="H1176" s="4" t="n">
@@ -43945,30 +43941,30 @@
     </row>
     <row r="1177">
       <c r="A1177" s="2" t="n">
-        <v>46006</v>
+        <v>46003</v>
       </c>
       <c r="B1177" s="3" t="inlineStr">
         <is>
-          <t>5107 · Travel - Other (Direct)</t>
+          <t>5123 · Auto fuel (Direct)</t>
         </is>
       </c>
       <c r="C1177" s="5" t="n">
-        <v>395.19</v>
+        <v>44.35</v>
       </c>
       <c r="D1177" s="3" t="inlineStr">
         <is>
           <t>Credit Card Charge</t>
         </is>
       </c>
-      <c r="E1177" s="3" t="inlineStr"/>
-      <c r="F1177" s="3" t="inlineStr">
-        <is>
-          <t>Luke Giguere	Flight- CVG to BGR 12/19</t>
-        </is>
-      </c>
+      <c r="E1177" s="3" t="inlineStr">
+        <is>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="F1177" s="3" t="inlineStr"/>
       <c r="G1177" s="3" t="inlineStr">
         <is>
-          <t>2310 · American Express Delta</t>
+          <t>2323 · Shell Credit Card - WEX</t>
         </is>
       </c>
       <c r="H1177" s="4" t="n">
@@ -43981,30 +43977,26 @@
       </c>
       <c r="B1178" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5107 · Travel - Other (Direct)</t>
         </is>
       </c>
       <c r="C1178" s="5" t="n">
-        <v>99.84</v>
+        <v>395.19</v>
       </c>
       <c r="D1178" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
-        </is>
-      </c>
-      <c r="E1178" s="3" t="inlineStr">
-        <is>
-          <t>56880259</t>
-        </is>
-      </c>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="E1178" s="3" t="inlineStr"/>
       <c r="F1178" s="3" t="inlineStr">
         <is>
-          <t>120V AC Float Switch for Sump Pumps</t>
+          <t>Luke Giguere	Flight- CVG to BGR 12/19</t>
         </is>
       </c>
       <c r="G1178" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>2310 · American Express Delta</t>
         </is>
       </c>
       <c r="H1178" s="4" t="n">
@@ -44021,7 +44013,7 @@
         </is>
       </c>
       <c r="C1179" s="5" t="n">
-        <v>7.74</v>
+        <v>99.84</v>
       </c>
       <c r="D1179" s="3" t="inlineStr">
         <is>
@@ -44035,7 +44027,7 @@
       </c>
       <c r="F1179" s="3" t="inlineStr">
         <is>
-          <t>TAx</t>
+          <t>120V AC Float Switch for Sump Pumps</t>
         </is>
       </c>
       <c r="G1179" s="3" t="inlineStr">
@@ -44053,11 +44045,11 @@
       </c>
       <c r="B1180" s="3" t="inlineStr">
         <is>
-          <t>5121 · Freight &amp; Shipping (Direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C1180" s="5" t="n">
-        <v>10.68</v>
+        <v>7.74</v>
       </c>
       <c r="D1180" s="3" t="inlineStr">
         <is>
@@ -44071,7 +44063,7 @@
       </c>
       <c r="F1180" s="3" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>TAx</t>
         </is>
       </c>
       <c r="G1180" s="3" t="inlineStr">
@@ -44085,15 +44077,15 @@
     </row>
     <row r="1181">
       <c r="A1181" s="2" t="n">
-        <v>46007</v>
+        <v>46006</v>
       </c>
       <c r="B1181" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5121 · Freight &amp; Shipping (Direct)</t>
         </is>
       </c>
       <c r="C1181" s="5" t="n">
-        <v>13.5</v>
+        <v>10.68</v>
       </c>
       <c r="D1181" s="3" t="inlineStr">
         <is>
@@ -44102,12 +44094,12 @@
       </c>
       <c r="E1181" s="3" t="inlineStr">
         <is>
-          <t>18726639</t>
+          <t>56880259</t>
         </is>
       </c>
       <c r="F1181" s="3" t="inlineStr">
         <is>
-          <t>AutomationDirect relay socket, 35mm</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="G1181" s="3" t="inlineStr">
@@ -44129,7 +44121,7 @@
         </is>
       </c>
       <c r="C1182" s="5" t="n">
-        <v>1.05</v>
+        <v>13.5</v>
       </c>
       <c r="D1182" s="3" t="inlineStr">
         <is>
@@ -44143,7 +44135,7 @@
       </c>
       <c r="F1182" s="3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>AutomationDirect relay socket, 35mm</t>
         </is>
       </c>
       <c r="G1182" s="3" t="inlineStr">
@@ -44165,7 +44157,7 @@
         </is>
       </c>
       <c r="C1183" s="5" t="n">
-        <v>26.18</v>
+        <v>1.05</v>
       </c>
       <c r="D1183" s="3" t="inlineStr">
         <is>
@@ -44174,12 +44166,12 @@
       </c>
       <c r="E1183" s="3" t="inlineStr">
         <is>
-          <t>16713191-00</t>
+          <t>18726639</t>
         </is>
       </c>
       <c r="F1183" s="3" t="inlineStr">
         <is>
-          <t>NC BLUE LEAK DETECTOR 32 OZ SPRAY</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="G1183" s="3" t="inlineStr">
@@ -44201,7 +44193,7 @@
         </is>
       </c>
       <c r="C1184" s="5" t="n">
-        <v>36.14</v>
+        <v>26.18</v>
       </c>
       <c r="D1184" s="3" t="inlineStr">
         <is>
@@ -44215,7 +44207,7 @@
       </c>
       <c r="F1184" s="3" t="inlineStr">
         <is>
-          <t>NC BLUE LEAK DETECTOR 1 GAL BTL</t>
+          <t>NC BLUE LEAK DETECTOR 32 OZ SPRAY</t>
         </is>
       </c>
       <c r="G1184" s="3" t="inlineStr">
@@ -44237,7 +44229,7 @@
         </is>
       </c>
       <c r="C1185" s="5" t="n">
-        <v>26.31</v>
+        <v>36.14</v>
       </c>
       <c r="D1185" s="3" t="inlineStr">
         <is>
@@ -44251,7 +44243,7 @@
       </c>
       <c r="F1185" s="3" t="inlineStr">
         <is>
-          <t>NRP 12" TONGUE &amp; GROOVE ADJUSTABLE PLIERS</t>
+          <t>NC BLUE LEAK DETECTOR 1 GAL BTL</t>
         </is>
       </c>
       <c r="G1185" s="3" t="inlineStr">
@@ -44273,7 +44265,7 @@
         </is>
       </c>
       <c r="C1186" s="5" t="n">
-        <v>22.29</v>
+        <v>26.31</v>
       </c>
       <c r="D1186" s="3" t="inlineStr">
         <is>
@@ -44287,7 +44279,7 @@
       </c>
       <c r="F1186" s="3" t="inlineStr">
         <is>
-          <t>NRP 9-1/2" T &amp; G #420 ADJUSTABLE PLIERS</t>
+          <t>NRP 12" TONGUE &amp; GROOVE ADJUSTABLE PLIERS</t>
         </is>
       </c>
       <c r="G1186" s="3" t="inlineStr">
@@ -44309,7 +44301,7 @@
         </is>
       </c>
       <c r="C1187" s="5" t="n">
-        <v>8.65</v>
+        <v>22.29</v>
       </c>
       <c r="D1187" s="3" t="inlineStr">
         <is>
@@ -44323,7 +44315,7 @@
       </c>
       <c r="F1187" s="3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>NRP 9-1/2" T &amp; G #420 ADJUSTABLE PLIERS</t>
         </is>
       </c>
       <c r="G1187" s="3" t="inlineStr">
@@ -44337,7 +44329,7 @@
     </row>
     <row r="1188">
       <c r="A1188" s="2" t="n">
-        <v>46008</v>
+        <v>46007</v>
       </c>
       <c r="B1188" s="3" t="inlineStr">
         <is>
@@ -44345,7 +44337,7 @@
         </is>
       </c>
       <c r="C1188" s="5" t="n">
-        <v>202</v>
+        <v>8.65</v>
       </c>
       <c r="D1188" s="3" t="inlineStr">
         <is>
@@ -44354,12 +44346,12 @@
       </c>
       <c r="E1188" s="3" t="inlineStr">
         <is>
-          <t>1126680</t>
+          <t>16713191-00</t>
         </is>
       </c>
       <c r="F1188" s="3" t="inlineStr">
         <is>
-          <t>1X1/2 BLK MI 150# RED COUP</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="G1188" s="3" t="inlineStr">
@@ -44377,30 +44369,26 @@
       </c>
       <c r="B1189" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5105 · Travel - Airfare (Direct)</t>
         </is>
       </c>
       <c r="C1189" s="5" t="n">
-        <v>23.35</v>
+        <v>548.1799999999999</v>
       </c>
       <c r="D1189" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
-        </is>
-      </c>
-      <c r="E1189" s="3" t="inlineStr">
-        <is>
-          <t>1126680</t>
-        </is>
-      </c>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="E1189" s="3" t="inlineStr"/>
       <c r="F1189" s="3" t="inlineStr">
         <is>
-          <t>1/2X1000 MEGATAPE</t>
+          <t>Ohio	Tony Madrid	Flight- CVG to HLN 12/19</t>
         </is>
       </c>
       <c r="G1189" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>2313. · Chase Mileage Plus CW (5726)</t>
         </is>
       </c>
       <c r="H1189" s="4" t="n">
@@ -44417,7 +44405,7 @@
         </is>
       </c>
       <c r="C1190" s="5" t="n">
-        <v>89.76000000000001</v>
+        <v>202</v>
       </c>
       <c r="D1190" s="3" t="inlineStr">
         <is>
@@ -44431,7 +44419,7 @@
       </c>
       <c r="F1190" s="3" t="inlineStr">
         <is>
-          <t>12 STRT PIPE WRCH</t>
+          <t>1X1/2 BLK MI 150# RED COUP</t>
         </is>
       </c>
       <c r="G1190" s="3" t="inlineStr">
@@ -44453,7 +44441,7 @@
         </is>
       </c>
       <c r="C1191" s="5" t="n">
-        <v>158.98</v>
+        <v>23.35</v>
       </c>
       <c r="D1191" s="3" t="inlineStr">
         <is>
@@ -44467,7 +44455,7 @@
       </c>
       <c r="F1191" s="3" t="inlineStr">
         <is>
-          <t>14 ALUM STRT PIPE WRCH 814</t>
+          <t>1/2X1000 MEGATAPE</t>
         </is>
       </c>
       <c r="G1191" s="3" t="inlineStr">
@@ -44489,7 +44477,7 @@
         </is>
       </c>
       <c r="C1192" s="5" t="n">
-        <v>129.75</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="D1192" s="3" t="inlineStr">
         <is>
@@ -44503,7 +44491,7 @@
       </c>
       <c r="F1192" s="3" t="inlineStr">
         <is>
-          <t>1 PT SOFT SET GASOILA</t>
+          <t>12 STRT PIPE WRCH</t>
         </is>
       </c>
       <c r="G1192" s="3" t="inlineStr">
@@ -44525,7 +44513,7 @@
         </is>
       </c>
       <c r="C1193" s="5" t="n">
-        <v>195.36</v>
+        <v>158.98</v>
       </c>
       <c r="D1193" s="3" t="inlineStr">
         <is>
@@ -44539,7 +44527,7 @@
       </c>
       <c r="F1193" s="3" t="inlineStr">
         <is>
-          <t>LF 1/2 BRS 600# WOG THRD 2PC BV</t>
+          <t>14 ALUM STRT PIPE WRCH 814</t>
         </is>
       </c>
       <c r="G1193" s="3" t="inlineStr">
@@ -44561,7 +44549,7 @@
         </is>
       </c>
       <c r="C1194" s="5" t="n">
-        <v>62.25</v>
+        <v>129.75</v>
       </c>
       <c r="D1194" s="3" t="inlineStr">
         <is>
@@ -44575,7 +44563,7 @@
       </c>
       <c r="F1194" s="3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>1 PT SOFT SET GASOILA</t>
         </is>
       </c>
       <c r="G1194" s="3" t="inlineStr">
@@ -44593,11 +44581,11 @@
       </c>
       <c r="B1195" s="3" t="inlineStr">
         <is>
-          <t>5115 · Rent - Equipment (direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C1195" s="5" t="n">
-        <v>4639</v>
+        <v>195.36</v>
       </c>
       <c r="D1195" s="3" t="inlineStr">
         <is>
@@ -44606,12 +44594,12 @@
       </c>
       <c r="E1195" s="3" t="inlineStr">
         <is>
-          <t>250412474-006</t>
+          <t>1126680</t>
         </is>
       </c>
       <c r="F1195" s="3" t="inlineStr">
         <is>
-          <t>FORKLIFT VARIABLE REACH 10000# 50'-62'</t>
+          <t>LF 1/2 BRS 600# WOG THRD 2PC BV</t>
         </is>
       </c>
       <c r="G1195" s="3" t="inlineStr">
@@ -44629,11 +44617,11 @@
       </c>
       <c r="B1196" s="3" t="inlineStr">
         <is>
-          <t>5115 · Rent - Equipment (direct)</t>
-        </is>
-      </c>
-      <c r="C1196" s="3" t="n">
-        <v>0</v>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1196" s="5" t="n">
+        <v>62.25</v>
       </c>
       <c r="D1196" s="3" t="inlineStr">
         <is>
@@ -44642,12 +44630,12 @@
       </c>
       <c r="E1196" s="3" t="inlineStr">
         <is>
-          <t>250412474-006</t>
+          <t>1126680</t>
         </is>
       </c>
       <c r="F1196" s="3" t="inlineStr">
         <is>
-          <t>Delivery &amp; Pick up charge</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="G1196" s="3" t="inlineStr">
@@ -44669,7 +44657,7 @@
         </is>
       </c>
       <c r="C1197" s="5" t="n">
-        <v>461.86</v>
+        <v>4639</v>
       </c>
       <c r="D1197" s="3" t="inlineStr">
         <is>
@@ -44683,7 +44671,7 @@
       </c>
       <c r="F1197" s="3" t="inlineStr">
         <is>
-          <t>Service Charge and Tax</t>
+          <t>FORKLIFT VARIABLE REACH 10000# 50'-62'</t>
         </is>
       </c>
       <c r="G1197" s="3" t="inlineStr">
@@ -44697,30 +44685,34 @@
     </row>
     <row r="1198">
       <c r="A1198" s="2" t="n">
-        <v>46010</v>
+        <v>46008</v>
       </c>
       <c r="B1198" s="3" t="inlineStr">
         <is>
-          <t>5107.1 · Travel - Car Rental</t>
-        </is>
-      </c>
-      <c r="C1198" s="5" t="n">
-        <v>1042.93</v>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C1198" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D1198" s="3" t="inlineStr">
         <is>
-          <t>Credit Card Charge</t>
-        </is>
-      </c>
-      <c r="E1198" s="3" t="inlineStr"/>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1198" s="3" t="inlineStr">
+        <is>
+          <t>250412474-006</t>
+        </is>
+      </c>
       <c r="F1198" s="3" t="inlineStr">
         <is>
-          <t>B Krumbholz 12/8 - 12/19</t>
+          <t>Delivery &amp; Pick up charge</t>
         </is>
       </c>
       <c r="G1198" s="3" t="inlineStr">
         <is>
-          <t>2321 · Commerce Bank - Enterprise Acct</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="H1198" s="4" t="n">
@@ -44729,34 +44721,34 @@
     </row>
     <row r="1199">
       <c r="A1199" s="2" t="n">
-        <v>46010</v>
+        <v>46008</v>
       </c>
       <c r="B1199" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5115 · Rent - Equipment (direct)</t>
         </is>
       </c>
       <c r="C1199" s="5" t="n">
-        <v>150</v>
+        <v>461.86</v>
       </c>
       <c r="D1199" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E1199" s="3" t="inlineStr">
         <is>
-          <t>16804</t>
+          <t>250412474-006</t>
         </is>
       </c>
       <c r="F1199" s="3" t="inlineStr">
         <is>
-          <t>Andy Remillard Per diem for week of 12/22/2025 - 12/24/2025</t>
+          <t>Service Charge and Tax</t>
         </is>
       </c>
       <c r="G1199" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="H1199" s="4" t="n">
@@ -44765,30 +44757,30 @@
     </row>
     <row r="1200">
       <c r="A1200" s="2" t="n">
-        <v>46016</v>
+        <v>46010</v>
       </c>
       <c r="B1200" s="3" t="inlineStr">
         <is>
-          <t>5121 · Freight &amp; Shipping (Direct)</t>
+          <t>5107.1 · Travel - Car Rental</t>
         </is>
       </c>
       <c r="C1200" s="5" t="n">
-        <v>341.76</v>
+        <v>1042.93</v>
       </c>
       <c r="D1200" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
-        </is>
-      </c>
-      <c r="E1200" s="3" t="inlineStr">
-        <is>
-          <t>886937985460</t>
-        </is>
-      </c>
-      <c r="F1200" s="3" t="inlineStr"/>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="E1200" s="3" t="inlineStr"/>
+      <c r="F1200" s="3" t="inlineStr">
+        <is>
+          <t>B Krumbholz 12/8 - 12/19</t>
+        </is>
+      </c>
       <c r="G1200" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>2321 · Commerce Bank - Enterprise Acct</t>
         </is>
       </c>
       <c r="H1200" s="4" t="n">
@@ -44797,7 +44789,7 @@
     </row>
     <row r="1201">
       <c r="A1201" s="2" t="n">
-        <v>46021</v>
+        <v>46010</v>
       </c>
       <c r="B1201" s="3" t="inlineStr">
         <is>
@@ -44814,12 +44806,12 @@
       </c>
       <c r="E1201" s="3" t="inlineStr">
         <is>
-          <t>16807</t>
+          <t>16804</t>
         </is>
       </c>
       <c r="F1201" s="3" t="inlineStr">
         <is>
-          <t>Andy Remillard Per diem for week of 12/29/2025 - 1/4/2026</t>
+          <t>Andy Remillard Per diem for week of 12/22/2025 - 12/24/2025</t>
         </is>
       </c>
       <c r="G1201" s="3" t="inlineStr">
@@ -44833,34 +44825,34 @@
     </row>
     <row r="1202">
       <c r="A1202" s="2" t="n">
-        <v>46021</v>
+        <v>46013</v>
       </c>
       <c r="B1202" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C1202" s="5" t="n">
-        <v>150</v>
+        <v>282.56</v>
       </c>
       <c r="D1202" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E1202" s="3" t="inlineStr">
         <is>
-          <t>16807</t>
+          <t>9750496094</t>
         </is>
       </c>
       <c r="F1202" s="3" t="inlineStr">
         <is>
-          <t>Mike Cogswell Per diem for week of 12/29/2025 - 1/4/2026</t>
+          <t xml:space="preserve"> NEUTRAL KIT, 600V AC</t>
         </is>
       </c>
       <c r="G1202" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="H1202" s="4" t="n">
@@ -44869,34 +44861,34 @@
     </row>
     <row r="1203">
       <c r="A1203" s="2" t="n">
-        <v>46028</v>
+        <v>46013</v>
       </c>
       <c r="B1203" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C1203" s="5" t="n">
-        <v>350</v>
+        <v>144.18</v>
       </c>
       <c r="D1203" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E1203" s="3" t="inlineStr">
         <is>
-          <t>16808</t>
+          <t>9750496094</t>
         </is>
       </c>
       <c r="F1203" s="3" t="inlineStr">
         <is>
-          <t>Andy Remillard Per diem for week of 1/5/2026 - 1/11/2026</t>
+          <t xml:space="preserve"> GROUND KIT, 400 A; 600 A, 600V AC</t>
         </is>
       </c>
       <c r="G1203" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="H1203" s="4" t="n">
@@ -44905,34 +44897,34 @@
     </row>
     <row r="1204">
       <c r="A1204" s="2" t="n">
-        <v>46028</v>
+        <v>46013</v>
       </c>
       <c r="B1204" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C1204" s="5" t="n">
-        <v>350</v>
+        <v>28.81</v>
       </c>
       <c r="D1204" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E1204" s="3" t="inlineStr">
         <is>
-          <t>16808</t>
+          <t>9750496094</t>
         </is>
       </c>
       <c r="F1204" s="3" t="inlineStr">
         <is>
-          <t>Mike Cogswell Per diem for week of 1/5/2026 - 1/11/2026</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="G1204" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="H1204" s="4" t="n">
@@ -44941,34 +44933,30 @@
     </row>
     <row r="1205">
       <c r="A1205" s="2" t="n">
-        <v>46028</v>
+        <v>46016</v>
       </c>
       <c r="B1205" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5105 · Travel - Airfare (Direct)</t>
         </is>
       </c>
       <c r="C1205" s="5" t="n">
-        <v>100</v>
+        <v>363.45</v>
       </c>
       <c r="D1205" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
-        </is>
-      </c>
-      <c r="E1205" s="3" t="inlineStr">
-        <is>
-          <t>16808</t>
-        </is>
-      </c>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="E1205" s="3" t="inlineStr"/>
       <c r="F1205" s="3" t="inlineStr">
         <is>
-          <t>Mike Cogswell Per diem for week of 12/20/25 - 12/21/25</t>
+          <t>Ohio	Mike Cogswell	Flight- BRG to CVG 1/2</t>
         </is>
       </c>
       <c r="G1205" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2313. · Chase Mileage Plus CW (5726)</t>
         </is>
       </c>
       <c r="H1205" s="4" t="n">
@@ -44977,34 +44965,30 @@
     </row>
     <row r="1206">
       <c r="A1206" s="2" t="n">
-        <v>46028</v>
+        <v>46016</v>
       </c>
       <c r="B1206" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5121 · Freight &amp; Shipping (Direct)</t>
         </is>
       </c>
       <c r="C1206" s="5" t="n">
-        <v>100</v>
+        <v>341.76</v>
       </c>
       <c r="D1206" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E1206" s="3" t="inlineStr">
         <is>
-          <t>16808</t>
-        </is>
-      </c>
-      <c r="F1206" s="3" t="inlineStr">
-        <is>
-          <t>Tony Madrid Per diem for week 12/20/2025 - 12/21/2025</t>
-        </is>
-      </c>
+          <t>886937985460</t>
+        </is>
+      </c>
+      <c r="F1206" s="3" t="inlineStr"/>
       <c r="G1206" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="H1206" s="4" t="n">
@@ -45013,7 +44997,7 @@
     </row>
     <row r="1207">
       <c r="A1207" s="2" t="n">
-        <v>46028</v>
+        <v>46021</v>
       </c>
       <c r="B1207" s="3" t="inlineStr">
         <is>
@@ -45021,7 +45005,7 @@
         </is>
       </c>
       <c r="C1207" s="5" t="n">
-        <v>700</v>
+        <v>150</v>
       </c>
       <c r="D1207" s="3" t="inlineStr">
         <is>
@@ -45030,12 +45014,12 @@
       </c>
       <c r="E1207" s="3" t="inlineStr">
         <is>
-          <t>16808</t>
+          <t>16807</t>
         </is>
       </c>
       <c r="F1207" s="3" t="inlineStr">
         <is>
-          <t>Vace Varasteh Per diem for week of 12/29/2025 - 1/11/2026</t>
+          <t>Andy Remillard Per diem for week of 12/29/2025 - 1/4/2026</t>
         </is>
       </c>
       <c r="G1207" s="3" t="inlineStr">
@@ -45049,34 +45033,34 @@
     </row>
     <row r="1208">
       <c r="A1208" s="2" t="n">
-        <v>46028</v>
+        <v>46021</v>
       </c>
       <c r="B1208" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
         </is>
       </c>
       <c r="C1208" s="5" t="n">
-        <v>484.56</v>
+        <v>150</v>
       </c>
       <c r="D1208" s="3" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>General Journal</t>
         </is>
       </c>
       <c r="E1208" s="3" t="inlineStr">
         <is>
-          <t>ER 122926</t>
+          <t>16807</t>
         </is>
       </c>
       <c r="F1208" s="3" t="inlineStr">
         <is>
-          <t>Home Depot</t>
+          <t>Mike Cogswell Per diem for week of 12/29/2025 - 1/4/2026</t>
         </is>
       </c>
       <c r="G1208" s="3" t="inlineStr">
         <is>
-          <t>1006.1 · (NEW) Calif B &amp; T Checking</t>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
         </is>
       </c>
       <c r="H1208" s="4" t="n">
@@ -45085,34 +45069,30 @@
     </row>
     <row r="1209">
       <c r="A1209" s="2" t="n">
-        <v>46028</v>
+        <v>46026</v>
       </c>
       <c r="B1209" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5123 · Auto fuel (Direct)</t>
         </is>
       </c>
       <c r="C1209" s="5" t="n">
-        <v>426.99</v>
+        <v>46.67</v>
       </c>
       <c r="D1209" s="3" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Credit Card Charge</t>
         </is>
       </c>
       <c r="E1209" s="3" t="inlineStr">
         <is>
-          <t>ER 122926</t>
-        </is>
-      </c>
-      <c r="F1209" s="3" t="inlineStr">
-        <is>
-          <t>Costco</t>
-        </is>
-      </c>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="F1209" s="3" t="inlineStr"/>
       <c r="G1209" s="3" t="inlineStr">
         <is>
-          <t>1006.1 · (NEW) Calif B &amp; T Checking</t>
+          <t>2323 · Shell Credit Card - WEX</t>
         </is>
       </c>
       <c r="H1209" s="4" t="n">
@@ -45125,30 +45105,30 @@
       </c>
       <c r="B1210" s="3" t="inlineStr">
         <is>
-          <t>5115 · Rent - Equipment (direct)</t>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
         </is>
       </c>
       <c r="C1210" s="5" t="n">
-        <v>2076</v>
+        <v>350</v>
       </c>
       <c r="D1210" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>General Journal</t>
         </is>
       </c>
       <c r="E1210" s="3" t="inlineStr">
         <is>
-          <t>250412474-007</t>
+          <t>16808</t>
         </is>
       </c>
       <c r="F1210" s="3" t="inlineStr">
         <is>
-          <t>FORKLIFT VARIABLE REACH 10000# 50'-62'</t>
+          <t>Andy Remillard Per diem for week of 1/5/2026 - 1/11/2026</t>
         </is>
       </c>
       <c r="G1210" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
         </is>
       </c>
       <c r="H1210" s="4" t="n">
@@ -45161,30 +45141,30 @@
       </c>
       <c r="B1211" s="3" t="inlineStr">
         <is>
-          <t>5115 · Rent - Equipment (direct)</t>
-        </is>
-      </c>
-      <c r="C1211" s="3" t="n">
-        <v>0</v>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
+        </is>
+      </c>
+      <c r="C1211" s="5" t="n">
+        <v>350</v>
       </c>
       <c r="D1211" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>General Journal</t>
         </is>
       </c>
       <c r="E1211" s="3" t="inlineStr">
         <is>
-          <t>250412474-007</t>
+          <t>16808</t>
         </is>
       </c>
       <c r="F1211" s="3" t="inlineStr">
         <is>
-          <t>Delivery &amp; Pick up charge</t>
+          <t>Mike Cogswell Per diem for week of 1/5/2026 - 1/11/2026</t>
         </is>
       </c>
       <c r="G1211" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
         </is>
       </c>
       <c r="H1211" s="4" t="n">
@@ -45197,30 +45177,30 @@
       </c>
       <c r="B1212" s="3" t="inlineStr">
         <is>
-          <t>5115 · Rent - Equipment (direct)</t>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
         </is>
       </c>
       <c r="C1212" s="5" t="n">
-        <v>408.82</v>
+        <v>100</v>
       </c>
       <c r="D1212" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>General Journal</t>
         </is>
       </c>
       <c r="E1212" s="3" t="inlineStr">
         <is>
-          <t>250412474-007</t>
+          <t>16808</t>
         </is>
       </c>
       <c r="F1212" s="3" t="inlineStr">
         <is>
-          <t>Service Charge and Tax</t>
+          <t>Mike Cogswell Per diem for week of 12/20/25 - 12/21/25</t>
         </is>
       </c>
       <c r="G1212" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
         </is>
       </c>
       <c r="H1212" s="4" t="n">
@@ -45233,30 +45213,30 @@
       </c>
       <c r="B1213" s="3" t="inlineStr">
         <is>
-          <t>5115 · Rent - Equipment (direct)</t>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
         </is>
       </c>
       <c r="C1213" s="5" t="n">
-        <v>1972</v>
+        <v>100</v>
       </c>
       <c r="D1213" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>General Journal</t>
         </is>
       </c>
       <c r="E1213" s="3" t="inlineStr">
         <is>
-          <t>254738310-003</t>
+          <t>16808</t>
         </is>
       </c>
       <c r="F1213" s="3" t="inlineStr">
         <is>
-          <t>SKID STEER TRACK LOADER 1700-1999#</t>
+          <t>Tony Madrid Per diem for week 12/20/2025 - 12/21/2025</t>
         </is>
       </c>
       <c r="G1213" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
         </is>
       </c>
       <c r="H1213" s="4" t="n">
@@ -45269,30 +45249,30 @@
       </c>
       <c r="B1214" s="3" t="inlineStr">
         <is>
-          <t>5115 · Rent - Equipment (direct)</t>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
         </is>
       </c>
       <c r="C1214" s="5" t="n">
-        <v>39.44</v>
+        <v>700</v>
       </c>
       <c r="D1214" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>General Journal</t>
         </is>
       </c>
       <c r="E1214" s="3" t="inlineStr">
         <is>
-          <t>254738310-003</t>
+          <t>16808</t>
         </is>
       </c>
       <c r="F1214" s="3" t="inlineStr">
         <is>
-          <t>Environmental Charge</t>
+          <t>Vace Varasteh Per diem for week of 12/29/2025 - 1/11/2026</t>
         </is>
       </c>
       <c r="G1214" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
         </is>
       </c>
       <c r="H1214" s="4" t="n">
@@ -45305,30 +45285,30 @@
       </c>
       <c r="B1215" s="3" t="inlineStr">
         <is>
-          <t>5115 · Rent - Equipment (direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C1215" s="5" t="n">
-        <v>156.9</v>
+        <v>484.56</v>
       </c>
       <c r="D1215" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="E1215" s="3" t="inlineStr">
         <is>
-          <t>254738310-003</t>
+          <t>ER 122926</t>
         </is>
       </c>
       <c r="F1215" s="3" t="inlineStr">
         <is>
-          <t>Taxes &amp; Fees</t>
+          <t>Home Depot</t>
         </is>
       </c>
       <c r="G1215" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>1006.1 · (NEW) Calif B &amp; T Checking</t>
         </is>
       </c>
       <c r="H1215" s="4" t="n">
@@ -45341,30 +45321,30 @@
       </c>
       <c r="B1216" s="3" t="inlineStr">
         <is>
-          <t>5115 · Rent - Equipment (direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C1216" s="5" t="n">
-        <v>561</v>
+        <v>426.99</v>
       </c>
       <c r="D1216" s="3" t="inlineStr">
         <is>
-          <t>Bill</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="E1216" s="3" t="inlineStr">
         <is>
-          <t>256400488-002</t>
+          <t>ER 122926</t>
         </is>
       </c>
       <c r="F1216" s="3" t="inlineStr">
         <is>
-          <t>PV2412532S OFFICE TRAILER 8X24</t>
+          <t>Costco</t>
         </is>
       </c>
       <c r="G1216" s="3" t="inlineStr">
         <is>
-          <t>2000 · Accounts Payable</t>
+          <t>1006.1 · (NEW) Calif B &amp; T Checking</t>
         </is>
       </c>
       <c r="H1216" s="4" t="n">
@@ -45381,7 +45361,7 @@
         </is>
       </c>
       <c r="C1217" s="5" t="n">
-        <v>66.5</v>
+        <v>2076</v>
       </c>
       <c r="D1217" s="3" t="inlineStr">
         <is>
@@ -45390,12 +45370,12 @@
       </c>
       <c r="E1217" s="3" t="inlineStr">
         <is>
-          <t>256400488-002</t>
+          <t>250412474-007</t>
         </is>
       </c>
       <c r="F1217" s="3" t="inlineStr">
         <is>
-          <t>OFFICE TRAILER STEPS</t>
+          <t>FORKLIFT VARIABLE REACH 10000# 50'-62'</t>
         </is>
       </c>
       <c r="G1217" s="3" t="inlineStr">
@@ -45426,12 +45406,12 @@
       </c>
       <c r="E1218" s="3" t="inlineStr">
         <is>
-          <t>256400488-002</t>
+          <t>250412474-007</t>
         </is>
       </c>
       <c r="F1218" s="3" t="inlineStr">
         <is>
-          <t>BLOCK AND LEVEL + INSTALL OF 4 ANCHORS</t>
+          <t>Delivery &amp; Pick up charge</t>
         </is>
       </c>
       <c r="G1218" s="3" t="inlineStr">
@@ -45452,8 +45432,8 @@
           <t>5115 · Rent - Equipment (direct)</t>
         </is>
       </c>
-      <c r="C1219" s="3" t="n">
-        <v>0</v>
+      <c r="C1219" s="5" t="n">
+        <v>408.82</v>
       </c>
       <c r="D1219" s="3" t="inlineStr">
         <is>
@@ -45462,12 +45442,12 @@
       </c>
       <c r="E1219" s="3" t="inlineStr">
         <is>
-          <t>256400488-002</t>
+          <t>250412474-007</t>
         </is>
       </c>
       <c r="F1219" s="3" t="inlineStr">
         <is>
-          <t>Delivery &amp; PIck Up Charge</t>
+          <t>Service Charge and Tax</t>
         </is>
       </c>
       <c r="G1219" s="3" t="inlineStr">
@@ -45488,8 +45468,8 @@
           <t>5115 · Rent - Equipment (direct)</t>
         </is>
       </c>
-      <c r="C1220" s="3" t="n">
-        <v>0</v>
+      <c r="C1220" s="5" t="n">
+        <v>1972</v>
       </c>
       <c r="D1220" s="3" t="inlineStr">
         <is>
@@ -45498,12 +45478,12 @@
       </c>
       <c r="E1220" s="3" t="inlineStr">
         <is>
-          <t>256400488-002</t>
+          <t>254738310-003</t>
         </is>
       </c>
       <c r="F1220" s="3" t="inlineStr">
         <is>
-          <t>Tear Down</t>
+          <t>SKID STEER TRACK LOADER 1700-1999#</t>
         </is>
       </c>
       <c r="G1220" s="3" t="inlineStr">
@@ -45525,7 +45505,7 @@
         </is>
       </c>
       <c r="C1221" s="5" t="n">
-        <v>48.95</v>
+        <v>39.44</v>
       </c>
       <c r="D1221" s="3" t="inlineStr">
         <is>
@@ -45534,12 +45514,12 @@
       </c>
       <c r="E1221" s="3" t="inlineStr">
         <is>
-          <t>256400488-002</t>
+          <t>254738310-003</t>
         </is>
       </c>
       <c r="F1221" s="3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Environmental Charge</t>
         </is>
       </c>
       <c r="G1221" s="3" t="inlineStr">
@@ -45553,15 +45533,15 @@
     </row>
     <row r="1222">
       <c r="A1222" s="2" t="n">
-        <v>46030</v>
+        <v>46028</v>
       </c>
       <c r="B1222" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5115 · Rent - Equipment (direct)</t>
         </is>
       </c>
       <c r="C1222" s="5" t="n">
-        <v>926.54</v>
+        <v>156.9</v>
       </c>
       <c r="D1222" s="3" t="inlineStr">
         <is>
@@ -45570,12 +45550,12 @@
       </c>
       <c r="E1222" s="3" t="inlineStr">
         <is>
-          <t>1202362</t>
+          <t>254738310-003</t>
         </is>
       </c>
       <c r="F1222" s="3" t="inlineStr">
         <is>
-          <t>LF 4 CI 200# BRZ EPDM LUG BFV LO</t>
+          <t>Taxes &amp; Fees</t>
         </is>
       </c>
       <c r="G1222" s="3" t="inlineStr">
@@ -45589,15 +45569,15 @@
     </row>
     <row r="1223">
       <c r="A1223" s="2" t="n">
-        <v>46030</v>
+        <v>46028</v>
       </c>
       <c r="B1223" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5115 · Rent - Equipment (direct)</t>
         </is>
       </c>
       <c r="C1223" s="5" t="n">
-        <v>29.28</v>
+        <v>561</v>
       </c>
       <c r="D1223" s="3" t="inlineStr">
         <is>
@@ -45606,12 +45586,12 @@
       </c>
       <c r="E1223" s="3" t="inlineStr">
         <is>
-          <t>1202362</t>
+          <t>256400488-002</t>
         </is>
       </c>
       <c r="F1223" s="3" t="inlineStr">
         <is>
-          <t>1/2 OD X 1/2 MIP FLR UNION</t>
+          <t>PV2412532S OFFICE TRAILER 8X24</t>
         </is>
       </c>
       <c r="G1223" s="3" t="inlineStr">
@@ -45625,15 +45605,15 @@
     </row>
     <row r="1224">
       <c r="A1224" s="2" t="n">
-        <v>46030</v>
+        <v>46028</v>
       </c>
       <c r="B1224" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
+          <t>5115 · Rent - Equipment (direct)</t>
         </is>
       </c>
       <c r="C1224" s="5" t="n">
-        <v>48.1</v>
+        <v>66.5</v>
       </c>
       <c r="D1224" s="3" t="inlineStr">
         <is>
@@ -45642,12 +45622,12 @@
       </c>
       <c r="E1224" s="3" t="inlineStr">
         <is>
-          <t>1202362</t>
+          <t>256400488-002</t>
         </is>
       </c>
       <c r="F1224" s="3" t="inlineStr">
         <is>
-          <t>4 ZN 150# DBL SIDE LUG BFV BLT SET</t>
+          <t>OFFICE TRAILER STEPS</t>
         </is>
       </c>
       <c r="G1224" s="3" t="inlineStr">
@@ -45661,15 +45641,15 @@
     </row>
     <row r="1225">
       <c r="A1225" s="2" t="n">
-        <v>46030</v>
+        <v>46028</v>
       </c>
       <c r="B1225" s="3" t="inlineStr">
         <is>
-          <t>5111 · Parts &amp; material costs (Direct)</t>
-        </is>
-      </c>
-      <c r="C1225" s="5" t="n">
-        <v>78.3</v>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C1225" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D1225" s="3" t="inlineStr">
         <is>
@@ -45678,12 +45658,12 @@
       </c>
       <c r="E1225" s="3" t="inlineStr">
         <is>
-          <t>1202362</t>
+          <t>256400488-002</t>
         </is>
       </c>
       <c r="F1225" s="3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>BLOCK AND LEVEL + INSTALL OF 4 ANCHORS</t>
         </is>
       </c>
       <c r="G1225" s="3" t="inlineStr">
@@ -45697,34 +45677,34 @@
     </row>
     <row r="1226">
       <c r="A1226" s="2" t="n">
-        <v>46034</v>
+        <v>46028</v>
       </c>
       <c r="B1226" s="3" t="inlineStr">
         <is>
-          <t>5106 · Travel - Hotel (Direct)</t>
-        </is>
-      </c>
-      <c r="C1226" s="5" t="n">
-        <v>62.08</v>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C1226" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D1226" s="3" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E1226" s="3" t="inlineStr">
         <is>
-          <t>ER 01.012.2</t>
+          <t>256400488-002</t>
         </is>
       </c>
       <c r="F1226" s="3" t="inlineStr">
         <is>
-          <t>Hotel in Cinc</t>
+          <t>Delivery &amp; PIck Up Charge</t>
         </is>
       </c>
       <c r="G1226" s="3" t="inlineStr">
         <is>
-          <t>1006.1 · (NEW) Calif B &amp; T Checking</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="H1226" s="4" t="n">
@@ -45733,34 +45713,34 @@
     </row>
     <row r="1227">
       <c r="A1227" s="2" t="n">
-        <v>46038</v>
+        <v>46028</v>
       </c>
       <c r="B1227" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
-        </is>
-      </c>
-      <c r="C1227" s="5" t="n">
-        <v>700</v>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C1227" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D1227" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E1227" s="3" t="inlineStr">
         <is>
-          <t>16810</t>
+          <t>256400488-002</t>
         </is>
       </c>
       <c r="F1227" s="3" t="inlineStr">
         <is>
-          <t>Andy Remillard Per diem for week of 1/12/2026 - 1/25/2026</t>
+          <t>Tear Down</t>
         </is>
       </c>
       <c r="G1227" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="H1227" s="4" t="n">
@@ -45769,34 +45749,34 @@
     </row>
     <row r="1228">
       <c r="A1228" s="2" t="n">
-        <v>46038</v>
+        <v>46028</v>
       </c>
       <c r="B1228" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5115 · Rent - Equipment (direct)</t>
         </is>
       </c>
       <c r="C1228" s="5" t="n">
-        <v>1000</v>
+        <v>48.95</v>
       </c>
       <c r="D1228" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E1228" s="3" t="inlineStr">
         <is>
-          <t>16810</t>
+          <t>256400488-002</t>
         </is>
       </c>
       <c r="F1228" s="3" t="inlineStr">
         <is>
-          <t>Brian Krumbholz Per diem for week of 1/6/2026 - 1/25/2026</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="G1228" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="H1228" s="4" t="n">
@@ -45805,34 +45785,30 @@
     </row>
     <row r="1229">
       <c r="A1229" s="2" t="n">
-        <v>46038</v>
+        <v>46028</v>
       </c>
       <c r="B1229" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5123 · Auto fuel (Direct)</t>
         </is>
       </c>
       <c r="C1229" s="5" t="n">
-        <v>100</v>
+        <v>28.89</v>
       </c>
       <c r="D1229" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
+          <t>Credit Card Charge</t>
         </is>
       </c>
       <c r="E1229" s="3" t="inlineStr">
         <is>
-          <t>16810</t>
-        </is>
-      </c>
-      <c r="F1229" s="3" t="inlineStr">
-        <is>
-          <t>Luke Giguere Per diem credit for 12/20/25 - 12/21/25</t>
-        </is>
-      </c>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="F1229" s="3" t="inlineStr"/>
       <c r="G1229" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2323 · Shell Credit Card - WEX</t>
         </is>
       </c>
       <c r="H1229" s="4" t="n">
@@ -45841,34 +45817,30 @@
     </row>
     <row r="1230">
       <c r="A1230" s="2" t="n">
-        <v>46038</v>
+        <v>46028</v>
       </c>
       <c r="B1230" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5123 · Auto fuel (Direct)</t>
         </is>
       </c>
       <c r="C1230" s="5" t="n">
-        <v>700</v>
+        <v>37.5</v>
       </c>
       <c r="D1230" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
+          <t>Credit Card Charge</t>
         </is>
       </c>
       <c r="E1230" s="3" t="inlineStr">
         <is>
-          <t>16810</t>
-        </is>
-      </c>
-      <c r="F1230" s="3" t="inlineStr">
-        <is>
-          <t>Mike Cogswell Per diem for week of 1/12/2026 - 1/25/2026</t>
-        </is>
-      </c>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="F1230" s="3" t="inlineStr"/>
       <c r="G1230" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2323 · Shell Credit Card - WEX</t>
         </is>
       </c>
       <c r="H1230" s="4" t="n">
@@ -45877,34 +45849,30 @@
     </row>
     <row r="1231">
       <c r="A1231" s="2" t="n">
-        <v>46038</v>
+        <v>46028</v>
       </c>
       <c r="B1231" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5123 · Auto fuel (Direct)</t>
         </is>
       </c>
       <c r="C1231" s="5" t="n">
-        <v>350</v>
+        <v>75.38</v>
       </c>
       <c r="D1231" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
+          <t>Credit Card Charge</t>
         </is>
       </c>
       <c r="E1231" s="3" t="inlineStr">
         <is>
-          <t>16810</t>
-        </is>
-      </c>
-      <c r="F1231" s="3" t="inlineStr">
-        <is>
-          <t>Tony Madrid Per diem for week of 1/19/2026 - 1/25/2026</t>
-        </is>
-      </c>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="F1231" s="3" t="inlineStr"/>
       <c r="G1231" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2323 · Shell Credit Card - WEX</t>
         </is>
       </c>
       <c r="H1231" s="4" t="n">
@@ -45913,34 +45881,34 @@
     </row>
     <row r="1232">
       <c r="A1232" s="2" t="n">
-        <v>46038</v>
+        <v>46029</v>
       </c>
       <c r="B1232" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C1232" s="5" t="n">
-        <v>650</v>
+        <v>23.29</v>
       </c>
       <c r="D1232" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E1232" s="3" t="inlineStr">
         <is>
-          <t>16810</t>
+          <t>CIN/019989</t>
         </is>
       </c>
       <c r="F1232" s="3" t="inlineStr">
         <is>
-          <t>Vu Tran Per diem for week of 1/6/2026 - 1/18/2026</t>
+          <t>5/8" x 8' GROUND ROD</t>
         </is>
       </c>
       <c r="G1232" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="H1232" s="4" t="n">
@@ -45949,34 +45917,34 @@
     </row>
     <row r="1233">
       <c r="A1233" s="2" t="n">
-        <v>46038</v>
+        <v>46029</v>
       </c>
       <c r="B1233" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C1233" s="5" t="n">
-        <v>100</v>
+        <v>49.31</v>
       </c>
       <c r="D1233" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E1233" s="3" t="inlineStr">
         <is>
-          <t>16810</t>
+          <t>CIN/019989</t>
         </is>
       </c>
       <c r="F1233" s="3" t="inlineStr">
         <is>
-          <t>Vu Tran Per diem credit for 11/22/25 - 11/23/25</t>
+          <t>4" 90 SCH40 PE ELBOW 078549</t>
         </is>
       </c>
       <c r="G1233" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="H1233" s="4" t="n">
@@ -45985,34 +45953,34 @@
     </row>
     <row r="1234">
       <c r="A1234" s="2" t="n">
-        <v>46038</v>
+        <v>46029</v>
       </c>
       <c r="B1234" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C1234" s="5" t="n">
-        <v>450</v>
+        <v>72.94</v>
       </c>
       <c r="D1234" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E1234" s="3" t="inlineStr">
         <is>
-          <t>16810</t>
+          <t>CIN/019989</t>
         </is>
       </c>
       <c r="F1234" s="3" t="inlineStr">
         <is>
-          <t>Wyatt Staples Per diem for week of 1/6/2026 - 1/14/2026</t>
+          <t>4" 45 SCH40 PE ELBOW 078561</t>
         </is>
       </c>
       <c r="G1234" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="H1234" s="4" t="n">
@@ -46021,7 +45989,7 @@
     </row>
     <row r="1235">
       <c r="A1235" s="2" t="n">
-        <v>46038</v>
+        <v>46029</v>
       </c>
       <c r="B1235" s="3" t="inlineStr">
         <is>
@@ -46029,7 +45997,7 @@
         </is>
       </c>
       <c r="C1235" s="5" t="n">
-        <v>80</v>
+        <v>10.17</v>
       </c>
       <c r="D1235" s="3" t="inlineStr">
         <is>
@@ -46038,12 +46006,12 @@
       </c>
       <c r="E1235" s="3" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>CIN/019989</t>
         </is>
       </c>
       <c r="F1235" s="3" t="inlineStr">
         <is>
-          <t>ISOBUTYLENE- 100 PPM CAL</t>
+          <t>CRIMP</t>
         </is>
       </c>
       <c r="G1235" s="3" t="inlineStr">
@@ -46057,7 +46025,7 @@
     </row>
     <row r="1236">
       <c r="A1236" s="2" t="n">
-        <v>46038</v>
+        <v>46029</v>
       </c>
       <c r="B1236" s="3" t="inlineStr">
         <is>
@@ -46065,7 +46033,7 @@
         </is>
       </c>
       <c r="C1236" s="5" t="n">
-        <v>250</v>
+        <v>6.6</v>
       </c>
       <c r="D1236" s="3" t="inlineStr">
         <is>
@@ -46074,12 +46042,12 @@
       </c>
       <c r="E1236" s="3" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>CIN/019989</t>
         </is>
       </c>
       <c r="F1236" s="3" t="inlineStr">
         <is>
-          <t>REGULTATOR- DEMAND FLOW,</t>
+          <t>CRIMP</t>
         </is>
       </c>
       <c r="G1236" s="3" t="inlineStr">
@@ -46093,7 +46061,7 @@
     </row>
     <row r="1237">
       <c r="A1237" s="2" t="n">
-        <v>46038</v>
+        <v>46029</v>
       </c>
       <c r="B1237" s="3" t="inlineStr">
         <is>
@@ -46101,7 +46069,7 @@
         </is>
       </c>
       <c r="C1237" s="5" t="n">
-        <v>25.58</v>
+        <v>3.7</v>
       </c>
       <c r="D1237" s="3" t="inlineStr">
         <is>
@@ -46110,12 +46078,12 @@
       </c>
       <c r="E1237" s="3" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>CIN/019989</t>
         </is>
       </c>
       <c r="F1237" s="3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>One Hole Tongue 14 AWG - 1/0 AWG</t>
         </is>
       </c>
       <c r="G1237" s="3" t="inlineStr">
@@ -46129,15 +46097,15 @@
     </row>
     <row r="1238">
       <c r="A1238" s="2" t="n">
-        <v>46038</v>
+        <v>46029</v>
       </c>
       <c r="B1238" s="3" t="inlineStr">
         <is>
-          <t>5121 · Freight &amp; Shipping (Direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C1238" s="5" t="n">
-        <v>30</v>
+        <v>2.81</v>
       </c>
       <c r="D1238" s="3" t="inlineStr">
         <is>
@@ -46146,12 +46114,12 @@
       </c>
       <c r="E1238" s="3" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>CIN/019989</t>
         </is>
       </c>
       <c r="F1238" s="3" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>CABLE CLAMP 1-1/4"</t>
         </is>
       </c>
       <c r="G1238" s="3" t="inlineStr">
@@ -46165,7 +46133,7 @@
     </row>
     <row r="1239">
       <c r="A1239" s="2" t="n">
-        <v>46042</v>
+        <v>46029</v>
       </c>
       <c r="B1239" s="3" t="inlineStr">
         <is>
@@ -46173,7 +46141,7 @@
         </is>
       </c>
       <c r="C1239" s="5" t="n">
-        <v>33.44</v>
+        <v>8.49</v>
       </c>
       <c r="D1239" s="3" t="inlineStr">
         <is>
@@ -46182,12 +46150,12 @@
       </c>
       <c r="E1239" s="3" t="inlineStr">
         <is>
-          <t>9168141852</t>
+          <t>CIN/019989</t>
         </is>
       </c>
       <c r="F1239" s="3" t="inlineStr">
         <is>
-          <t>Carbon Steel Electrode 5 lb Tube</t>
+          <t>078093 4" TERMINAL ADAPTER</t>
         </is>
       </c>
       <c r="G1239" s="3" t="inlineStr">
@@ -46201,7 +46169,7 @@
     </row>
     <row r="1240">
       <c r="A1240" s="2" t="n">
-        <v>46042</v>
+        <v>46029</v>
       </c>
       <c r="B1240" s="3" t="inlineStr">
         <is>
@@ -46209,7 +46177,7 @@
         </is>
       </c>
       <c r="C1240" s="5" t="n">
-        <v>10.16</v>
+        <v>4.85</v>
       </c>
       <c r="D1240" s="3" t="inlineStr">
         <is>
@@ -46218,12 +46186,12 @@
       </c>
       <c r="E1240" s="3" t="inlineStr">
         <is>
-          <t>9168141852</t>
+          <t>CIN/019989</t>
         </is>
       </c>
       <c r="F1240" s="3" t="inlineStr">
         <is>
-          <t>Chipping Hammer With 10 1/2" Coil Handle</t>
+          <t>WI PLASTIC BUSHING 4"</t>
         </is>
       </c>
       <c r="G1240" s="3" t="inlineStr">
@@ -46237,7 +46205,7 @@
     </row>
     <row r="1241">
       <c r="A1241" s="2" t="n">
-        <v>46042</v>
+        <v>46029</v>
       </c>
       <c r="B1241" s="3" t="inlineStr">
         <is>
@@ -46245,7 +46213,7 @@
         </is>
       </c>
       <c r="C1241" s="5" t="n">
-        <v>557.46</v>
+        <v>3.61</v>
       </c>
       <c r="D1241" s="3" t="inlineStr">
         <is>
@@ -46254,12 +46222,12 @@
       </c>
       <c r="E1241" s="3" t="inlineStr">
         <is>
-          <t>9168141852</t>
+          <t>CIN/019989</t>
         </is>
       </c>
       <c r="F1241" s="3" t="inlineStr">
         <is>
-          <t>Prene® Welding Cable 50' Pre-Cut Coil</t>
+          <t>WI STEEL LOCKNUT 4"</t>
         </is>
       </c>
       <c r="G1241" s="3" t="inlineStr">
@@ -46273,7 +46241,7 @@
     </row>
     <row r="1242">
       <c r="A1242" s="2" t="n">
-        <v>46042</v>
+        <v>46029</v>
       </c>
       <c r="B1242" s="3" t="inlineStr">
         <is>
@@ -46281,7 +46249,7 @@
         </is>
       </c>
       <c r="C1242" s="5" t="n">
-        <v>27.42</v>
+        <v>69.42</v>
       </c>
       <c r="D1242" s="3" t="inlineStr">
         <is>
@@ -46290,12 +46258,12 @@
       </c>
       <c r="E1242" s="3" t="inlineStr">
         <is>
-          <t>9168141852</t>
+          <t>CIN/019989</t>
         </is>
       </c>
       <c r="F1242" s="3" t="inlineStr">
         <is>
-          <t>CONNECTOR CABLE LC-40</t>
+          <t>THHN-1/0-BLK-19STR-CU</t>
         </is>
       </c>
       <c r="G1242" s="3" t="inlineStr">
@@ -46309,7 +46277,7 @@
     </row>
     <row r="1243">
       <c r="A1243" s="2" t="n">
-        <v>46042</v>
+        <v>46029</v>
       </c>
       <c r="B1243" s="3" t="inlineStr">
         <is>
@@ -46317,7 +46285,7 @@
         </is>
       </c>
       <c r="C1243" s="5" t="n">
-        <v>27.42</v>
+        <v>30.79</v>
       </c>
       <c r="D1243" s="3" t="inlineStr">
         <is>
@@ -46326,12 +46294,12 @@
       </c>
       <c r="E1243" s="3" t="inlineStr">
         <is>
-          <t>9168141852</t>
+          <t>CIN/019989</t>
         </is>
       </c>
       <c r="F1243" s="3" t="inlineStr">
         <is>
-          <t>LOCK-TIGHT ACTION LC-40 FEMALE HALF</t>
+          <t>(078010)4" COUPLING 078010</t>
         </is>
       </c>
       <c r="G1243" s="3" t="inlineStr">
@@ -46345,7 +46313,7 @@
     </row>
     <row r="1244">
       <c r="A1244" s="2" t="n">
-        <v>46042</v>
+        <v>46029</v>
       </c>
       <c r="B1244" s="3" t="inlineStr">
         <is>
@@ -46353,7 +46321,7 @@
         </is>
       </c>
       <c r="C1244" s="5" t="n">
-        <v>68.18000000000001</v>
+        <v>2.25</v>
       </c>
       <c r="D1244" s="3" t="inlineStr">
         <is>
@@ -46362,12 +46330,12 @@
       </c>
       <c r="E1244" s="3" t="inlineStr">
         <is>
-          <t>9168141852</t>
+          <t>CIN/019989</t>
         </is>
       </c>
       <c r="F1244" s="3" t="inlineStr">
         <is>
-          <t>Tax &amp; Fees</t>
+          <t>Green 3M Tape Temflex-165</t>
         </is>
       </c>
       <c r="G1244" s="3" t="inlineStr">
@@ -46381,7 +46349,7 @@
     </row>
     <row r="1245">
       <c r="A1245" s="2" t="n">
-        <v>46042</v>
+        <v>46029</v>
       </c>
       <c r="B1245" s="3" t="inlineStr">
         <is>
@@ -46389,7 +46357,7 @@
         </is>
       </c>
       <c r="C1245" s="5" t="n">
-        <v>111.96</v>
+        <v>22.49</v>
       </c>
       <c r="D1245" s="3" t="inlineStr">
         <is>
@@ -46398,12 +46366,12 @@
       </c>
       <c r="E1245" s="3" t="inlineStr">
         <is>
-          <t>CIN/020360</t>
+          <t>CIN/019989</t>
         </is>
       </c>
       <c r="F1245" s="3" t="inlineStr">
         <is>
-          <t>4" 90 SCH40 PE ELBOW 36" RAD</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="G1245" s="3" t="inlineStr">
@@ -46417,7 +46385,7 @@
     </row>
     <row r="1246">
       <c r="A1246" s="2" t="n">
-        <v>46042</v>
+        <v>46030</v>
       </c>
       <c r="B1246" s="3" t="inlineStr">
         <is>
@@ -46425,7 +46393,7 @@
         </is>
       </c>
       <c r="C1246" s="5" t="n">
-        <v>16.94</v>
+        <v>926.54</v>
       </c>
       <c r="D1246" s="3" t="inlineStr">
         <is>
@@ -46434,12 +46402,12 @@
       </c>
       <c r="E1246" s="3" t="inlineStr">
         <is>
-          <t>CIN/020360</t>
+          <t>1202362</t>
         </is>
       </c>
       <c r="F1246" s="3" t="inlineStr">
         <is>
-          <t>(078010)4" COUPLING 078010</t>
+          <t>LF 4 CI 200# BRZ EPDM LUG BFV LO</t>
         </is>
       </c>
       <c r="G1246" s="3" t="inlineStr">
@@ -46453,7 +46421,7 @@
     </row>
     <row r="1247">
       <c r="A1247" s="2" t="n">
-        <v>46042</v>
+        <v>46030</v>
       </c>
       <c r="B1247" s="3" t="inlineStr">
         <is>
@@ -46461,7 +46429,7 @@
         </is>
       </c>
       <c r="C1247" s="5" t="n">
-        <v>10.06</v>
+        <v>29.28</v>
       </c>
       <c r="D1247" s="3" t="inlineStr">
         <is>
@@ -46470,12 +46438,12 @@
       </c>
       <c r="E1247" s="3" t="inlineStr">
         <is>
-          <t>CIN/020360</t>
+          <t>1202362</t>
         </is>
       </c>
       <c r="F1247" s="3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>1/2 OD X 1/2 MIP FLR UNION</t>
         </is>
       </c>
       <c r="G1247" s="3" t="inlineStr">
@@ -46489,7 +46457,7 @@
     </row>
     <row r="1248">
       <c r="A1248" s="2" t="n">
-        <v>46042</v>
+        <v>46030</v>
       </c>
       <c r="B1248" s="3" t="inlineStr">
         <is>
@@ -46497,7 +46465,7 @@
         </is>
       </c>
       <c r="C1248" s="5" t="n">
-        <v>105.13</v>
+        <v>48.1</v>
       </c>
       <c r="D1248" s="3" t="inlineStr">
         <is>
@@ -46506,12 +46474,12 @@
       </c>
       <c r="E1248" s="3" t="inlineStr">
         <is>
-          <t>58443274</t>
+          <t>1202362</t>
         </is>
       </c>
       <c r="F1248" s="3" t="inlineStr">
         <is>
-          <t>Synthetic Air Compressor Oil, ISO Grade 220, 1-gal Jug</t>
+          <t>4 ZN 150# DBL SIDE LUG BFV BLT SET</t>
         </is>
       </c>
       <c r="G1248" s="3" t="inlineStr">
@@ -46525,7 +46493,7 @@
     </row>
     <row r="1249">
       <c r="A1249" s="2" t="n">
-        <v>46042</v>
+        <v>46030</v>
       </c>
       <c r="B1249" s="3" t="inlineStr">
         <is>
@@ -46533,7 +46501,7 @@
         </is>
       </c>
       <c r="C1249" s="5" t="n">
-        <v>22.92</v>
+        <v>78.3</v>
       </c>
       <c r="D1249" s="3" t="inlineStr">
         <is>
@@ -46542,10 +46510,14 @@
       </c>
       <c r="E1249" s="3" t="inlineStr">
         <is>
-          <t>58443274</t>
-        </is>
-      </c>
-      <c r="F1249" s="3" t="inlineStr"/>
+          <t>1202362</t>
+        </is>
+      </c>
+      <c r="F1249" s="3" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
       <c r="G1249" s="3" t="inlineStr">
         <is>
           <t>2000 · Accounts Payable</t>
@@ -46557,15 +46529,15 @@
     </row>
     <row r="1250">
       <c r="A1250" s="2" t="n">
-        <v>46042</v>
+        <v>46030</v>
       </c>
       <c r="B1250" s="3" t="inlineStr">
         <is>
-          <t>5128 · Health &amp; Safety Equip (Direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C1250" s="5" t="n">
-        <v>50.92</v>
+        <v>282.56</v>
       </c>
       <c r="D1250" s="3" t="inlineStr">
         <is>
@@ -46574,12 +46546,12 @@
       </c>
       <c r="E1250" s="3" t="inlineStr">
         <is>
-          <t>9168141852</t>
+          <t>9764598711</t>
         </is>
       </c>
       <c r="F1250" s="3" t="inlineStr">
         <is>
-          <t>Large 13" Green Deerskin FR Foam/Fleece</t>
+          <t>NEUTRAL KIT, 600V AC</t>
         </is>
       </c>
       <c r="G1250" s="3" t="inlineStr">
@@ -46593,7 +46565,7 @@
     </row>
     <row r="1251">
       <c r="A1251" s="2" t="n">
-        <v>46043</v>
+        <v>46030</v>
       </c>
       <c r="B1251" s="3" t="inlineStr">
         <is>
@@ -46601,7 +46573,7 @@
         </is>
       </c>
       <c r="C1251" s="5" t="n">
-        <v>74.36</v>
+        <v>19.08</v>
       </c>
       <c r="D1251" s="3" t="inlineStr">
         <is>
@@ -46610,12 +46582,12 @@
       </c>
       <c r="E1251" s="3" t="inlineStr">
         <is>
-          <t>94401343</t>
+          <t>9764598711</t>
         </is>
       </c>
       <c r="F1251" s="3" t="inlineStr">
         <is>
-          <t>|BOLTPAK 4" RING 150 1/8" NAS</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="G1251" s="3" t="inlineStr">
@@ -46629,7 +46601,7 @@
     </row>
     <row r="1252">
       <c r="A1252" s="2" t="n">
-        <v>46043</v>
+        <v>46031</v>
       </c>
       <c r="B1252" s="3" t="inlineStr">
         <is>
@@ -46637,7 +46609,7 @@
         </is>
       </c>
       <c r="C1252" s="5" t="n">
-        <v>4.09</v>
+        <v>107.84</v>
       </c>
       <c r="D1252" s="3" t="inlineStr">
         <is>
@@ -46646,12 +46618,12 @@
       </c>
       <c r="E1252" s="3" t="inlineStr">
         <is>
-          <t>94401343</t>
+          <t>9765464806</t>
         </is>
       </c>
       <c r="F1252" s="3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>FILLER PLATE,FLUSH,PK15</t>
         </is>
       </c>
       <c r="G1252" s="3" t="inlineStr">
@@ -46665,34 +46637,34 @@
     </row>
     <row r="1253">
       <c r="A1253" s="2" t="n">
-        <v>46045</v>
+        <v>46031</v>
       </c>
       <c r="B1253" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C1253" s="5" t="n">
-        <v>350</v>
+        <v>7.28</v>
       </c>
       <c r="D1253" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E1253" s="3" t="inlineStr">
         <is>
-          <t>16811</t>
+          <t>9765464806</t>
         </is>
       </c>
       <c r="F1253" s="3" t="inlineStr">
         <is>
-          <t>Andy Remillard per diem Per diem for week of 1/26/2026 - 2/21/2026</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="G1253" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="H1253" s="4" t="n">
@@ -46701,34 +46673,30 @@
     </row>
     <row r="1254">
       <c r="A1254" s="2" t="n">
-        <v>46045</v>
+        <v>46031</v>
       </c>
       <c r="B1254" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5123 · Auto fuel (Direct)</t>
         </is>
       </c>
       <c r="C1254" s="5" t="n">
-        <v>350</v>
+        <v>55.92</v>
       </c>
       <c r="D1254" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
+          <t>Credit Card Charge</t>
         </is>
       </c>
       <c r="E1254" s="3" t="inlineStr">
         <is>
-          <t>16811</t>
-        </is>
-      </c>
-      <c r="F1254" s="3" t="inlineStr">
-        <is>
-          <t>Brian Krumbholz per diem Per diem for week of 1/26/2026 - 2/21/2026</t>
-        </is>
-      </c>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="F1254" s="3" t="inlineStr"/>
       <c r="G1254" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2323 · Shell Credit Card - WEX</t>
         </is>
       </c>
       <c r="H1254" s="4" t="n">
@@ -46737,34 +46705,30 @@
     </row>
     <row r="1255">
       <c r="A1255" s="2" t="n">
-        <v>46045</v>
+        <v>46033</v>
       </c>
       <c r="B1255" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5123 · Auto fuel (Direct)</t>
         </is>
       </c>
       <c r="C1255" s="5" t="n">
-        <v>350</v>
+        <v>45.09</v>
       </c>
       <c r="D1255" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
+          <t>Credit Card Charge</t>
         </is>
       </c>
       <c r="E1255" s="3" t="inlineStr">
         <is>
-          <t>16811</t>
-        </is>
-      </c>
-      <c r="F1255" s="3" t="inlineStr">
-        <is>
-          <t>Mike Cogswell per diem Per diem for week of 1/26/2026 - 2/21/2026</t>
-        </is>
-      </c>
+          <t>AR</t>
+        </is>
+      </c>
+      <c r="F1255" s="3" t="inlineStr"/>
       <c r="G1255" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>2323 · Shell Credit Card - WEX</t>
         </is>
       </c>
       <c r="H1255" s="4" t="n">
@@ -46773,34 +46737,34 @@
     </row>
     <row r="1256">
       <c r="A1256" s="2" t="n">
-        <v>46045</v>
+        <v>46034</v>
       </c>
       <c r="B1256" s="3" t="inlineStr">
         <is>
-          <t>5108 · Meals &amp; entertainment (Direct)</t>
+          <t>5106 · Travel - Hotel (Direct)</t>
         </is>
       </c>
       <c r="C1256" s="5" t="n">
-        <v>350</v>
+        <v>62.08</v>
       </c>
       <c r="D1256" s="3" t="inlineStr">
         <is>
-          <t>General Journal</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="E1256" s="3" t="inlineStr">
         <is>
-          <t>16811</t>
+          <t>ER 01.012.2</t>
         </is>
       </c>
       <c r="F1256" s="3" t="inlineStr">
         <is>
-          <t>Tony Madrid per diem Per diem for week of 1/26/2026 - 2/21/2026</t>
+          <t>Hotel in Cinc</t>
         </is>
       </c>
       <c r="G1256" s="3" t="inlineStr">
         <is>
-          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+          <t>1006.1 · (NEW) Calif B &amp; T Checking</t>
         </is>
       </c>
       <c r="H1256" s="4" t="n">
@@ -46809,34 +46773,34 @@
     </row>
     <row r="1257">
       <c r="A1257" s="2" t="n">
-        <v>46053</v>
+        <v>46036</v>
       </c>
       <c r="B1257" s="3" t="inlineStr">
         <is>
-          <t>5115 · Rent - Equipment (direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C1257" s="5" t="n">
-        <v>561</v>
+        <v>23.34</v>
       </c>
       <c r="D1257" s="3" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E1257" s="3" t="inlineStr">
         <is>
-          <t>CIN25-006</t>
+          <t>9771091882</t>
         </is>
       </c>
       <c r="F1257" s="3" t="inlineStr">
         <is>
-          <t>PV2412532S OFFICE TRAILER 8X24</t>
+          <t>BLOCKCOVER,POLYCARBONATE,1POLE,1.7INW</t>
         </is>
       </c>
       <c r="G1257" s="3" t="inlineStr">
         <is>
-          <t>1100 · Trade Debtors</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="H1257" s="4" t="n">
@@ -46845,34 +46809,34 @@
     </row>
     <row r="1258">
       <c r="A1258" s="2" t="n">
-        <v>46053</v>
+        <v>46036</v>
       </c>
       <c r="B1258" s="3" t="inlineStr">
         <is>
-          <t>5115 · Rent - Equipment (direct)</t>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
         </is>
       </c>
       <c r="C1258" s="5" t="n">
-        <v>66.5</v>
+        <v>1.57</v>
       </c>
       <c r="D1258" s="3" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>Bill</t>
         </is>
       </c>
       <c r="E1258" s="3" t="inlineStr">
         <is>
-          <t>CIN25-006</t>
+          <t>9771091882</t>
         </is>
       </c>
       <c r="F1258" s="3" t="inlineStr">
         <is>
-          <t>OFFICE TRAILER STEPS</t>
+          <t>Tax</t>
         </is>
       </c>
       <c r="G1258" s="3" t="inlineStr">
         <is>
-          <t>1100 · Trade Debtors</t>
+          <t>2000 · Accounts Payable</t>
         </is>
       </c>
       <c r="H1258" s="4" t="n">
@@ -46881,34 +46845,34 @@
     </row>
     <row r="1259">
       <c r="A1259" s="2" t="n">
-        <v>46053</v>
+        <v>46038</v>
       </c>
       <c r="B1259" s="3" t="inlineStr">
         <is>
-          <t>5115 · Rent - Equipment (direct)</t>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
         </is>
       </c>
       <c r="C1259" s="5" t="n">
-        <v>570</v>
+        <v>700</v>
       </c>
       <c r="D1259" s="3" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>General Journal</t>
         </is>
       </c>
       <c r="E1259" s="3" t="inlineStr">
         <is>
-          <t>CIN25-006</t>
+          <t>16810</t>
         </is>
       </c>
       <c r="F1259" s="3" t="inlineStr">
         <is>
-          <t>BLOCK AND LEVEL + INSTALL OF 4 ANCHORS</t>
+          <t>Andy Remillard Per diem for week of 1/12/2026 - 1/25/2026</t>
         </is>
       </c>
       <c r="G1259" s="3" t="inlineStr">
         <is>
-          <t>1100 · Trade Debtors</t>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
         </is>
       </c>
       <c r="H1259" s="4" t="n">
@@ -46917,34 +46881,34 @@
     </row>
     <row r="1260">
       <c r="A1260" s="2" t="n">
-        <v>46053</v>
+        <v>46038</v>
       </c>
       <c r="B1260" s="3" t="inlineStr">
         <is>
-          <t>5115 · Rent - Equipment (direct)</t>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
         </is>
       </c>
       <c r="C1260" s="5" t="n">
-        <v>710</v>
+        <v>1000</v>
       </c>
       <c r="D1260" s="3" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>General Journal</t>
         </is>
       </c>
       <c r="E1260" s="3" t="inlineStr">
         <is>
-          <t>CIN25-006</t>
+          <t>16810</t>
         </is>
       </c>
       <c r="F1260" s="3" t="inlineStr">
         <is>
-          <t>Delivery &amp; PIck Up Charge</t>
+          <t>Brian Krumbholz Per diem for week of 1/6/2026 - 1/25/2026</t>
         </is>
       </c>
       <c r="G1260" s="3" t="inlineStr">
         <is>
-          <t>1100 · Trade Debtors</t>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
         </is>
       </c>
       <c r="H1260" s="4" t="n">
@@ -46953,34 +46917,34 @@
     </row>
     <row r="1261">
       <c r="A1261" s="2" t="n">
-        <v>46053</v>
+        <v>46038</v>
       </c>
       <c r="B1261" s="3" t="inlineStr">
         <is>
-          <t>5115 · Rent - Equipment (direct)</t>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
         </is>
       </c>
       <c r="C1261" s="5" t="n">
-        <v>375</v>
+        <v>100</v>
       </c>
       <c r="D1261" s="3" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>General Journal</t>
         </is>
       </c>
       <c r="E1261" s="3" t="inlineStr">
         <is>
-          <t>CIN25-006</t>
+          <t>16810</t>
         </is>
       </c>
       <c r="F1261" s="3" t="inlineStr">
         <is>
-          <t>Tear Down</t>
+          <t>Luke Giguere Per diem credit for 12/20/25 - 12/21/25</t>
         </is>
       </c>
       <c r="G1261" s="3" t="inlineStr">
         <is>
-          <t>1100 · Trade Debtors</t>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
         </is>
       </c>
       <c r="H1261" s="4" t="n">
@@ -46989,34 +46953,34 @@
     </row>
     <row r="1262">
       <c r="A1262" s="2" t="n">
-        <v>46053</v>
+        <v>46038</v>
       </c>
       <c r="B1262" s="3" t="inlineStr">
         <is>
-          <t>5115 · Rent - Equipment (direct)</t>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
         </is>
       </c>
       <c r="C1262" s="5" t="n">
-        <v>168.12</v>
+        <v>700</v>
       </c>
       <c r="D1262" s="3" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>General Journal</t>
         </is>
       </c>
       <c r="E1262" s="3" t="inlineStr">
         <is>
-          <t>CIN25-006</t>
+          <t>16810</t>
         </is>
       </c>
       <c r="F1262" s="3" t="inlineStr">
         <is>
-          <t>Tax</t>
+          <t>Mike Cogswell Per diem for week of 1/12/2026 - 1/25/2026</t>
         </is>
       </c>
       <c r="G1262" s="3" t="inlineStr">
         <is>
-          <t>1100 · Trade Debtors</t>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
         </is>
       </c>
       <c r="H1262" s="4" t="n">
@@ -47025,34 +46989,34 @@
     </row>
     <row r="1263">
       <c r="A1263" s="2" t="n">
-        <v>46053</v>
+        <v>46038</v>
       </c>
       <c r="B1263" s="3" t="inlineStr">
         <is>
-          <t>5115 · Rent - Equipment (direct)</t>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
         </is>
       </c>
       <c r="C1263" s="5" t="n">
-        <v>561</v>
+        <v>350</v>
       </c>
       <c r="D1263" s="3" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>General Journal</t>
         </is>
       </c>
       <c r="E1263" s="3" t="inlineStr">
         <is>
-          <t>CIN25-006</t>
+          <t>16810</t>
         </is>
       </c>
       <c r="F1263" s="3" t="inlineStr">
         <is>
-          <t>PV2412532S OFFICE TRAILER 8X24</t>
+          <t>Tony Madrid Per diem for week of 1/19/2026 - 1/25/2026</t>
         </is>
       </c>
       <c r="G1263" s="3" t="inlineStr">
         <is>
-          <t>1100 · Trade Debtors</t>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
         </is>
       </c>
       <c r="H1263" s="4" t="n">
@@ -47061,34 +47025,34 @@
     </row>
     <row r="1264">
       <c r="A1264" s="2" t="n">
-        <v>46053</v>
+        <v>46038</v>
       </c>
       <c r="B1264" s="3" t="inlineStr">
         <is>
-          <t>5115 · Rent - Equipment (direct)</t>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
         </is>
       </c>
       <c r="C1264" s="5" t="n">
-        <v>66.5</v>
+        <v>650</v>
       </c>
       <c r="D1264" s="3" t="inlineStr">
         <is>
-          <t>Invoice</t>
+          <t>General Journal</t>
         </is>
       </c>
       <c r="E1264" s="3" t="inlineStr">
         <is>
-          <t>CIN25-006</t>
+          <t>16810</t>
         </is>
       </c>
       <c r="F1264" s="3" t="inlineStr">
         <is>
-          <t>OFFICE TRAILER STEPS</t>
+          <t>Vu Tran Per diem for week of 1/6/2026 - 1/18/2026</t>
         </is>
       </c>
       <c r="G1264" s="3" t="inlineStr">
         <is>
-          <t>1100 · Trade Debtors</t>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
         </is>
       </c>
       <c r="H1264" s="4" t="n">
@@ -47097,38 +47061,2942 @@
     </row>
     <row r="1265">
       <c r="A1265" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B1265" s="3" t="inlineStr">
+        <is>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
+        </is>
+      </c>
+      <c r="C1265" s="5" t="n">
+        <v>100</v>
+      </c>
+      <c r="D1265" s="3" t="inlineStr">
+        <is>
+          <t>General Journal</t>
+        </is>
+      </c>
+      <c r="E1265" s="3" t="inlineStr">
+        <is>
+          <t>16810</t>
+        </is>
+      </c>
+      <c r="F1265" s="3" t="inlineStr">
+        <is>
+          <t>Vu Tran Per diem credit for 11/22/25 - 11/23/25</t>
+        </is>
+      </c>
+      <c r="G1265" s="3" t="inlineStr">
+        <is>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+        </is>
+      </c>
+      <c r="H1265" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1266">
+      <c r="A1266" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B1266" s="3" t="inlineStr">
+        <is>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
+        </is>
+      </c>
+      <c r="C1266" s="5" t="n">
+        <v>450</v>
+      </c>
+      <c r="D1266" s="3" t="inlineStr">
+        <is>
+          <t>General Journal</t>
+        </is>
+      </c>
+      <c r="E1266" s="3" t="inlineStr">
+        <is>
+          <t>16810</t>
+        </is>
+      </c>
+      <c r="F1266" s="3" t="inlineStr">
+        <is>
+          <t>Wyatt Staples Per diem for week of 1/6/2026 - 1/14/2026</t>
+        </is>
+      </c>
+      <c r="G1266" s="3" t="inlineStr">
+        <is>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+        </is>
+      </c>
+      <c r="H1266" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1267">
+      <c r="A1267" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B1267" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1267" s="5" t="n">
+        <v>80</v>
+      </c>
+      <c r="D1267" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1267" s="3" t="inlineStr">
+        <is>
+          <t>10079</t>
+        </is>
+      </c>
+      <c r="F1267" s="3" t="inlineStr">
+        <is>
+          <t>ISOBUTYLENE- 100 PPM CAL</t>
+        </is>
+      </c>
+      <c r="G1267" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1267" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1268">
+      <c r="A1268" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B1268" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1268" s="5" t="n">
+        <v>250</v>
+      </c>
+      <c r="D1268" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1268" s="3" t="inlineStr">
+        <is>
+          <t>10079</t>
+        </is>
+      </c>
+      <c r="F1268" s="3" t="inlineStr">
+        <is>
+          <t>REGULTATOR- DEMAND FLOW,</t>
+        </is>
+      </c>
+      <c r="G1268" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1268" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1269">
+      <c r="A1269" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B1269" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1269" s="5" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="D1269" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1269" s="3" t="inlineStr">
+        <is>
+          <t>10079</t>
+        </is>
+      </c>
+      <c r="F1269" s="3" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="G1269" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1269" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1270">
+      <c r="A1270" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B1270" s="3" t="inlineStr">
+        <is>
+          <t>5121 · Freight &amp; Shipping (Direct)</t>
+        </is>
+      </c>
+      <c r="C1270" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D1270" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1270" s="3" t="inlineStr">
+        <is>
+          <t>10079</t>
+        </is>
+      </c>
+      <c r="F1270" s="3" t="inlineStr">
+        <is>
+          <t>Shipping</t>
+        </is>
+      </c>
+      <c r="G1270" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1270" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1271">
+      <c r="A1271" s="2" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B1271" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1271" s="5" t="n">
+        <v>111.96</v>
+      </c>
+      <c r="D1271" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1271" s="3" t="inlineStr">
+        <is>
+          <t>CIN/020360</t>
+        </is>
+      </c>
+      <c r="F1271" s="3" t="inlineStr">
+        <is>
+          <t>4" 90 SCH40 PE ELBOW 36" RAD</t>
+        </is>
+      </c>
+      <c r="G1271" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1271" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1272">
+      <c r="A1272" s="2" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B1272" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1272" s="5" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="D1272" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1272" s="3" t="inlineStr">
+        <is>
+          <t>CIN/020360</t>
+        </is>
+      </c>
+      <c r="F1272" s="3" t="inlineStr">
+        <is>
+          <t>(078010)4" COUPLING 078010</t>
+        </is>
+      </c>
+      <c r="G1272" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1272" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1273">
+      <c r="A1273" s="2" t="n">
+        <v>46041</v>
+      </c>
+      <c r="B1273" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1273" s="5" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="D1273" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1273" s="3" t="inlineStr">
+        <is>
+          <t>CIN/020360</t>
+        </is>
+      </c>
+      <c r="F1273" s="3" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="G1273" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1273" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1274">
+      <c r="A1274" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B1274" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1274" s="5" t="n">
+        <v>33.44</v>
+      </c>
+      <c r="D1274" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1274" s="3" t="inlineStr">
+        <is>
+          <t>9168141852</t>
+        </is>
+      </c>
+      <c r="F1274" s="3" t="inlineStr">
+        <is>
+          <t>Carbon Steel Electrode 5 lb Tube</t>
+        </is>
+      </c>
+      <c r="G1274" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1274" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1275">
+      <c r="A1275" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B1275" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1275" s="5" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="D1275" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1275" s="3" t="inlineStr">
+        <is>
+          <t>9168141852</t>
+        </is>
+      </c>
+      <c r="F1275" s="3" t="inlineStr">
+        <is>
+          <t>Chipping Hammer With 10 1/2" Coil Handle</t>
+        </is>
+      </c>
+      <c r="G1275" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1275" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1276">
+      <c r="A1276" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B1276" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1276" s="5" t="n">
+        <v>557.46</v>
+      </c>
+      <c r="D1276" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1276" s="3" t="inlineStr">
+        <is>
+          <t>9168141852</t>
+        </is>
+      </c>
+      <c r="F1276" s="3" t="inlineStr">
+        <is>
+          <t>Prene® Welding Cable 50' Pre-Cut Coil</t>
+        </is>
+      </c>
+      <c r="G1276" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1276" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1277">
+      <c r="A1277" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B1277" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1277" s="5" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="D1277" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1277" s="3" t="inlineStr">
+        <is>
+          <t>9168141852</t>
+        </is>
+      </c>
+      <c r="F1277" s="3" t="inlineStr">
+        <is>
+          <t>CONNECTOR CABLE LC-40</t>
+        </is>
+      </c>
+      <c r="G1277" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1277" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1278">
+      <c r="A1278" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B1278" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1278" s="5" t="n">
+        <v>27.42</v>
+      </c>
+      <c r="D1278" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1278" s="3" t="inlineStr">
+        <is>
+          <t>9168141852</t>
+        </is>
+      </c>
+      <c r="F1278" s="3" t="inlineStr">
+        <is>
+          <t>LOCK-TIGHT ACTION LC-40 FEMALE HALF</t>
+        </is>
+      </c>
+      <c r="G1278" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1278" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1279">
+      <c r="A1279" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B1279" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1279" s="5" t="n">
+        <v>68.18000000000001</v>
+      </c>
+      <c r="D1279" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1279" s="3" t="inlineStr">
+        <is>
+          <t>9168141852</t>
+        </is>
+      </c>
+      <c r="F1279" s="3" t="inlineStr">
+        <is>
+          <t>Tax &amp; Fees</t>
+        </is>
+      </c>
+      <c r="G1279" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1279" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1280">
+      <c r="A1280" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B1280" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1280" s="5" t="n">
+        <v>111.96</v>
+      </c>
+      <c r="D1280" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1280" s="3" t="inlineStr">
+        <is>
+          <t>CIN/020360</t>
+        </is>
+      </c>
+      <c r="F1280" s="3" t="inlineStr">
+        <is>
+          <t>4" 90 SCH40 PE ELBOW 36" RAD</t>
+        </is>
+      </c>
+      <c r="G1280" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1280" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1281">
+      <c r="A1281" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B1281" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1281" s="5" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="D1281" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1281" s="3" t="inlineStr">
+        <is>
+          <t>CIN/020360</t>
+        </is>
+      </c>
+      <c r="F1281" s="3" t="inlineStr">
+        <is>
+          <t>(078010)4" COUPLING 078010</t>
+        </is>
+      </c>
+      <c r="G1281" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1281" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1282">
+      <c r="A1282" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B1282" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1282" s="5" t="n">
+        <v>10.06</v>
+      </c>
+      <c r="D1282" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1282" s="3" t="inlineStr">
+        <is>
+          <t>CIN/020360</t>
+        </is>
+      </c>
+      <c r="F1282" s="3" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="G1282" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1282" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1283">
+      <c r="A1283" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B1283" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1283" s="5" t="n">
+        <v>105.13</v>
+      </c>
+      <c r="D1283" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1283" s="3" t="inlineStr">
+        <is>
+          <t>58443274</t>
+        </is>
+      </c>
+      <c r="F1283" s="3" t="inlineStr">
+        <is>
+          <t>Synthetic Air Compressor Oil, ISO Grade 220, 1-gal Jug</t>
+        </is>
+      </c>
+      <c r="G1283" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1283" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1284">
+      <c r="A1284" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B1284" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1284" s="5" t="n">
+        <v>22.92</v>
+      </c>
+      <c r="D1284" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1284" s="3" t="inlineStr">
+        <is>
+          <t>58443274</t>
+        </is>
+      </c>
+      <c r="F1284" s="3" t="inlineStr"/>
+      <c r="G1284" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1284" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1285">
+      <c r="A1285" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B1285" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1285" s="5" t="n">
+        <v>55.87</v>
+      </c>
+      <c r="D1285" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1285" s="3" t="inlineStr">
+        <is>
+          <t>0201184843</t>
+        </is>
+      </c>
+      <c r="F1285" s="3" t="inlineStr">
+        <is>
+          <t>6 YD FL/Load</t>
+        </is>
+      </c>
+      <c r="G1285" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1285" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1286">
+      <c r="A1286" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B1286" s="3" t="inlineStr">
+        <is>
+          <t>5128 · Health &amp; Safety Equip (Direct)</t>
+        </is>
+      </c>
+      <c r="C1286" s="5" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="D1286" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1286" s="3" t="inlineStr">
+        <is>
+          <t>9168141852</t>
+        </is>
+      </c>
+      <c r="F1286" s="3" t="inlineStr">
+        <is>
+          <t>Large 13" Green Deerskin FR Foam/Fleece</t>
+        </is>
+      </c>
+      <c r="G1286" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1286" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1287">
+      <c r="A1287" s="2" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B1287" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1287" s="5" t="n">
+        <v>74.36</v>
+      </c>
+      <c r="D1287" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1287" s="3" t="inlineStr">
+        <is>
+          <t>94401343</t>
+        </is>
+      </c>
+      <c r="F1287" s="3" t="inlineStr">
+        <is>
+          <t>|BOLTPAK 4" RING 150 1/8" NAS</t>
+        </is>
+      </c>
+      <c r="G1287" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1287" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1288">
+      <c r="A1288" s="2" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B1288" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1288" s="5" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="D1288" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1288" s="3" t="inlineStr">
+        <is>
+          <t>94401343</t>
+        </is>
+      </c>
+      <c r="F1288" s="3" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="G1288" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1288" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1289">
+      <c r="A1289" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B1289" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1289" s="5" t="n">
+        <v>55.36</v>
+      </c>
+      <c r="D1289" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1289" s="3" t="inlineStr">
+        <is>
+          <t>58607044</t>
+        </is>
+      </c>
+      <c r="F1289" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	Supplemental Eye Wash with Wall-Mount Station, Includes Two 32 oz. Bottles</t>
+        </is>
+      </c>
+      <c r="G1289" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1289" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1290">
+      <c r="A1290" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B1290" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1290" s="5" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="D1290" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1290" s="3" t="inlineStr">
+        <is>
+          <t>58607044</t>
+        </is>
+      </c>
+      <c r="F1290" s="3" t="inlineStr">
+        <is>
+          <t>tax</t>
+        </is>
+      </c>
+      <c r="G1290" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1290" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1291">
+      <c r="A1291" s="2" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B1291" s="3" t="inlineStr">
+        <is>
+          <t>5121 · Freight &amp; Shipping (Direct)</t>
+        </is>
+      </c>
+      <c r="C1291" s="5" t="n">
+        <v>16.34</v>
+      </c>
+      <c r="D1291" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1291" s="3" t="inlineStr">
+        <is>
+          <t>58607044</t>
+        </is>
+      </c>
+      <c r="F1291" s="3" t="inlineStr">
+        <is>
+          <t>Shipping</t>
+        </is>
+      </c>
+      <c r="G1291" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1291" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1292">
+      <c r="A1292" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B1292" s="3" t="inlineStr">
+        <is>
+          <t>5105 · Travel - Airfare (Direct)</t>
+        </is>
+      </c>
+      <c r="C1292" s="5" t="n">
+        <v>588.95</v>
+      </c>
+      <c r="D1292" s="3" t="inlineStr">
+        <is>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="E1292" s="3" t="inlineStr"/>
+      <c r="F1292" s="3" t="inlineStr">
+        <is>
+          <t>Ohio	Frank Allen	Flight- IAH to CVG 1/25- CVG to IAH 2/6</t>
+        </is>
+      </c>
+      <c r="G1292" s="3" t="inlineStr">
+        <is>
+          <t>2313. · Chase Mileage Plus CW (5726)</t>
+        </is>
+      </c>
+      <c r="H1292" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1293">
+      <c r="A1293" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B1293" s="3" t="inlineStr">
+        <is>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
+        </is>
+      </c>
+      <c r="C1293" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="D1293" s="3" t="inlineStr">
+        <is>
+          <t>General Journal</t>
+        </is>
+      </c>
+      <c r="E1293" s="3" t="inlineStr">
+        <is>
+          <t>16811</t>
+        </is>
+      </c>
+      <c r="F1293" s="3" t="inlineStr">
+        <is>
+          <t>Andy Remillard per diem Per diem for week of 1/26/2026 - 2/21/2026</t>
+        </is>
+      </c>
+      <c r="G1293" s="3" t="inlineStr">
+        <is>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+        </is>
+      </c>
+      <c r="H1293" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1294">
+      <c r="A1294" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B1294" s="3" t="inlineStr">
+        <is>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
+        </is>
+      </c>
+      <c r="C1294" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="D1294" s="3" t="inlineStr">
+        <is>
+          <t>General Journal</t>
+        </is>
+      </c>
+      <c r="E1294" s="3" t="inlineStr">
+        <is>
+          <t>16811</t>
+        </is>
+      </c>
+      <c r="F1294" s="3" t="inlineStr">
+        <is>
+          <t>Brian Krumbholz per diem Per diem for week of 1/26/2026 - 2/21/2026</t>
+        </is>
+      </c>
+      <c r="G1294" s="3" t="inlineStr">
+        <is>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+        </is>
+      </c>
+      <c r="H1294" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1295">
+      <c r="A1295" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B1295" s="3" t="inlineStr">
+        <is>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
+        </is>
+      </c>
+      <c r="C1295" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="D1295" s="3" t="inlineStr">
+        <is>
+          <t>General Journal</t>
+        </is>
+      </c>
+      <c r="E1295" s="3" t="inlineStr">
+        <is>
+          <t>16811</t>
+        </is>
+      </c>
+      <c r="F1295" s="3" t="inlineStr">
+        <is>
+          <t>Mike Cogswell per diem Per diem for week of 1/26/2026 - 2/21/2026</t>
+        </is>
+      </c>
+      <c r="G1295" s="3" t="inlineStr">
+        <is>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+        </is>
+      </c>
+      <c r="H1295" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1296">
+      <c r="A1296" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B1296" s="3" t="inlineStr">
+        <is>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
+        </is>
+      </c>
+      <c r="C1296" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="D1296" s="3" t="inlineStr">
+        <is>
+          <t>General Journal</t>
+        </is>
+      </c>
+      <c r="E1296" s="3" t="inlineStr">
+        <is>
+          <t>16811</t>
+        </is>
+      </c>
+      <c r="F1296" s="3" t="inlineStr">
+        <is>
+          <t>Tony Madrid per diem Per diem for week of 1/26/2026 - 2/21/2026</t>
+        </is>
+      </c>
+      <c r="G1296" s="3" t="inlineStr">
+        <is>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+        </is>
+      </c>
+      <c r="H1296" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1297">
+      <c r="A1297" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B1297" s="3" t="inlineStr">
+        <is>
+          <t>5120 · Outside services (Direct)</t>
+        </is>
+      </c>
+      <c r="C1297" s="5" t="n">
+        <v>143.96</v>
+      </c>
+      <c r="D1297" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1297" s="3" t="inlineStr">
+        <is>
+          <t>2993460</t>
+        </is>
+      </c>
+      <c r="F1297" s="3" t="inlineStr">
+        <is>
+          <t>Fluctuating Fuel Recovery</t>
+        </is>
+      </c>
+      <c r="G1297" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1297" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1298">
+      <c r="A1298" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B1298" s="3" t="inlineStr">
+        <is>
+          <t>5120 · Outside services (Direct)</t>
+        </is>
+      </c>
+      <c r="C1298" s="5" t="n">
+        <v>72.93000000000001</v>
+      </c>
+      <c r="D1298" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1298" s="3" t="inlineStr">
+        <is>
+          <t>2993460</t>
+        </is>
+      </c>
+      <c r="F1298" s="3" t="inlineStr">
+        <is>
+          <t>Supply Water</t>
+        </is>
+      </c>
+      <c r="G1298" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1298" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1299">
+      <c r="A1299" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B1299" s="3" t="inlineStr">
+        <is>
+          <t>5120 · Outside services (Direct)</t>
+        </is>
+      </c>
+      <c r="C1299" s="5" t="n">
+        <v>30.29</v>
+      </c>
+      <c r="D1299" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1299" s="3" t="inlineStr">
+        <is>
+          <t>2993460</t>
+        </is>
+      </c>
+      <c r="F1299" s="3" t="inlineStr">
+        <is>
+          <t>Consumable Materials</t>
+        </is>
+      </c>
+      <c r="G1299" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1299" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1300">
+      <c r="A1300" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B1300" s="3" t="inlineStr">
+        <is>
+          <t>5120 · Outside services (Direct)</t>
+        </is>
+      </c>
+      <c r="C1300" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1300" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1300" s="3" t="inlineStr">
+        <is>
+          <t>2993460</t>
+        </is>
+      </c>
+      <c r="F1300" s="3" t="inlineStr">
+        <is>
+          <t>Badger Hydrovac With Operator Overtime</t>
+        </is>
+      </c>
+      <c r="G1300" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1300" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1301">
+      <c r="A1301" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B1301" s="3" t="inlineStr">
+        <is>
+          <t>5120 · Outside services (Direct)</t>
+        </is>
+      </c>
+      <c r="C1301" s="5" t="n">
+        <v>1575.9</v>
+      </c>
+      <c r="D1301" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1301" s="3" t="inlineStr">
+        <is>
+          <t>2993460</t>
+        </is>
+      </c>
+      <c r="F1301" s="3" t="inlineStr">
+        <is>
+          <t>Badger Hydrovac With Operator</t>
+        </is>
+      </c>
+      <c r="G1301" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1301" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1302">
+      <c r="A1302" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B1302" s="3" t="inlineStr">
+        <is>
+          <t>5120 · Outside services (Direct)</t>
+        </is>
+      </c>
+      <c r="C1302" s="5" t="n">
+        <v>157.08</v>
+      </c>
+      <c r="D1302" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1302" s="3" t="inlineStr">
+        <is>
+          <t>2993460</t>
+        </is>
+      </c>
+      <c r="F1302" s="3" t="inlineStr">
+        <is>
+          <t>Disposition</t>
+        </is>
+      </c>
+      <c r="G1302" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1302" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1303">
+      <c r="A1303" s="2" t="n">
+        <v>46047</v>
+      </c>
+      <c r="B1303" s="3" t="inlineStr">
+        <is>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
+        </is>
+      </c>
+      <c r="C1303" s="5" t="n">
+        <v>468.28</v>
+      </c>
+      <c r="D1303" s="3" t="inlineStr">
+        <is>
+          <t>Credit Card Charge</t>
+        </is>
+      </c>
+      <c r="E1303" s="3" t="inlineStr"/>
+      <c r="F1303" s="3" t="inlineStr">
+        <is>
+          <t>Ohio	Tony Madrid	Flight- CVG tp HLN 1/30</t>
+        </is>
+      </c>
+      <c r="G1303" s="3" t="inlineStr">
+        <is>
+          <t>2313. · Chase Mileage Plus CW (5726)</t>
+        </is>
+      </c>
+      <c r="H1303" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1304">
+      <c r="A1304" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B1304" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1304" s="5" t="n">
+        <v>630</v>
+      </c>
+      <c r="D1304" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1304" s="3" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="F1304" s="3" t="inlineStr">
+        <is>
+          <t>TEDLAR BAG- 1L 50</t>
+        </is>
+      </c>
+      <c r="G1304" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1304" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1305">
+      <c r="A1305" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B1305" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1305" s="5" t="n">
+        <v>48.83</v>
+      </c>
+      <c r="D1305" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1305" s="3" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="F1305" s="3" t="inlineStr">
+        <is>
+          <t>tax</t>
+        </is>
+      </c>
+      <c r="G1305" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1305" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1306">
+      <c r="A1306" s="2" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B1306" s="3" t="inlineStr">
+        <is>
+          <t>5121 · Freight &amp; Shipping (Direct)</t>
+        </is>
+      </c>
+      <c r="C1306" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="D1306" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1306" s="3" t="inlineStr">
+        <is>
+          <t>10102</t>
+        </is>
+      </c>
+      <c r="F1306" s="3" t="inlineStr">
+        <is>
+          <t>Shipping</t>
+        </is>
+      </c>
+      <c r="G1306" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1306" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1307">
+      <c r="A1307" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B1307" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C1307" s="5" t="n">
+        <v>800</v>
+      </c>
+      <c r="D1307" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1307" s="3" t="inlineStr">
+        <is>
+          <t>19839</t>
+        </is>
+      </c>
+      <c r="F1307" s="3" t="inlineStr">
+        <is>
+          <t>Rental: HPAF 1000 Period: 1/19- 2/18</t>
+        </is>
+      </c>
+      <c r="G1307" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1307" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1308">
+      <c r="A1308" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B1308" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C1308" s="5" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D1308" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1308" s="3" t="inlineStr">
+        <is>
+          <t>19839</t>
+        </is>
+      </c>
+      <c r="F1308" s="3" t="inlineStr">
+        <is>
+          <t>Rental: VFV 3000 Period: 1/19- 2/18</t>
+        </is>
+      </c>
+      <c r="G1308" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1308" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1309">
+      <c r="A1309" s="2" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B1309" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C1309" s="5" t="n">
+        <v>300</v>
+      </c>
+      <c r="D1309" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1309" s="3" t="inlineStr">
+        <is>
+          <t>19839</t>
+        </is>
+      </c>
+      <c r="F1309" s="3" t="inlineStr">
+        <is>
+          <t>Rental: 4-Housing Pre Filter Skid Period 1/19-2/18</t>
+        </is>
+      </c>
+      <c r="G1309" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1309" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1310">
+      <c r="A1310" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B1310" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1310" s="5" t="n">
+        <v>128.88</v>
+      </c>
+      <c r="D1310" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1310" s="3" t="inlineStr">
+        <is>
+          <t>58948000</t>
+        </is>
+      </c>
+      <c r="F1310" s="3" t="inlineStr">
+        <is>
+          <t>Felt Filter Bag for Water, Sewn, 7" Diameter x 32" High, 10 Microns</t>
+        </is>
+      </c>
+      <c r="G1310" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1310" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1311">
+      <c r="A1311" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B1311" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1311" s="5" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="D1311" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1311" s="3" t="inlineStr">
+        <is>
+          <t>58948000</t>
+        </is>
+      </c>
+      <c r="F1311" s="3" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="G1311" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1311" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1312">
+      <c r="A1312" s="2" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B1312" s="3" t="inlineStr">
+        <is>
+          <t>5121 · Freight &amp; Shipping (Direct)</t>
+        </is>
+      </c>
+      <c r="C1312" s="5" t="n">
+        <v>17.26</v>
+      </c>
+      <c r="D1312" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1312" s="3" t="inlineStr">
+        <is>
+          <t>58948000</t>
+        </is>
+      </c>
+      <c r="F1312" s="3" t="inlineStr">
+        <is>
+          <t>Shipping</t>
+        </is>
+      </c>
+      <c r="G1312" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1312" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1313">
+      <c r="A1313" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B1313" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1313" s="5" t="n">
+        <v>72</v>
+      </c>
+      <c r="D1313" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1313" s="3" t="inlineStr">
+        <is>
+          <t>18883693</t>
+        </is>
+      </c>
+      <c r="F1313" s="3" t="inlineStr">
+        <is>
+          <t>ProSense mechanical pressure gauge,2.5in diameter, -30 to 0in Hg</t>
+        </is>
+      </c>
+      <c r="G1313" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1313" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1314">
+      <c r="A1314" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B1314" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1314" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1314" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1314" s="3" t="inlineStr">
+        <is>
+          <t>18883693</t>
+        </is>
+      </c>
+      <c r="F1314" s="3" t="inlineStr">
+        <is>
+          <t>ProSense mechanical pressure gauge, 2.5in diameter, 0 to 30 psig/0 to 200</t>
+        </is>
+      </c>
+      <c r="G1314" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1314" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1315">
+      <c r="A1315" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B1315" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1315" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="D1315" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1315" s="3" t="inlineStr">
+        <is>
+          <t>18883693</t>
+        </is>
+      </c>
+      <c r="F1315" s="3" t="inlineStr">
+        <is>
+          <t>ProSense mechanical pressure gauge, 2.5in diameter, 0 to 30 psig/0 to 400</t>
+        </is>
+      </c>
+      <c r="G1315" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1315" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1316">
+      <c r="A1316" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B1316" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1316" s="5" t="n">
+        <v>108</v>
+      </c>
+      <c r="D1316" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1316" s="3" t="inlineStr">
+        <is>
+          <t>18883693</t>
+        </is>
+      </c>
+      <c r="F1316" s="3" t="inlineStr">
+        <is>
+          <t>ProSense differential pressure gauge, 4in dial diameter, 0 to 50.0in of</t>
+        </is>
+      </c>
+      <c r="G1316" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1316" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1317">
+      <c r="A1317" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B1317" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1317" s="5" t="n">
+        <v>17.01</v>
+      </c>
+      <c r="D1317" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1317" s="3" t="inlineStr">
+        <is>
+          <t>18883693</t>
+        </is>
+      </c>
+      <c r="F1317" s="3" t="inlineStr">
+        <is>
+          <t>Sale Tax</t>
+        </is>
+      </c>
+      <c r="G1317" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1317" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1318">
+      <c r="A1318" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B1265" s="3" t="inlineStr">
+      <c r="B1318" s="3" t="inlineStr">
         <is>
           <t>5115 · Rent - Equipment (direct)</t>
         </is>
       </c>
-      <c r="C1265" s="5" t="n">
+      <c r="C1318" s="5" t="n">
+        <v>561</v>
+      </c>
+      <c r="D1318" s="3" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="E1318" s="3" t="inlineStr">
+        <is>
+          <t>CIN25-006</t>
+        </is>
+      </c>
+      <c r="F1318" s="3" t="inlineStr">
+        <is>
+          <t>PV2412532S OFFICE TRAILER 8X24</t>
+        </is>
+      </c>
+      <c r="G1318" s="3" t="inlineStr">
+        <is>
+          <t>1100 · Trade Debtors</t>
+        </is>
+      </c>
+      <c r="H1318" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1319">
+      <c r="A1319" s="2" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B1319" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C1319" s="5" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="D1319" s="3" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="E1319" s="3" t="inlineStr">
+        <is>
+          <t>CIN25-006</t>
+        </is>
+      </c>
+      <c r="F1319" s="3" t="inlineStr">
+        <is>
+          <t>OFFICE TRAILER STEPS</t>
+        </is>
+      </c>
+      <c r="G1319" s="3" t="inlineStr">
+        <is>
+          <t>1100 · Trade Debtors</t>
+        </is>
+      </c>
+      <c r="H1319" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1320">
+      <c r="A1320" s="2" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B1320" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C1320" s="5" t="n">
+        <v>570</v>
+      </c>
+      <c r="D1320" s="3" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="E1320" s="3" t="inlineStr">
+        <is>
+          <t>CIN25-006</t>
+        </is>
+      </c>
+      <c r="F1320" s="3" t="inlineStr">
+        <is>
+          <t>BLOCK AND LEVEL + INSTALL OF 4 ANCHORS</t>
+        </is>
+      </c>
+      <c r="G1320" s="3" t="inlineStr">
+        <is>
+          <t>1100 · Trade Debtors</t>
+        </is>
+      </c>
+      <c r="H1320" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1321">
+      <c r="A1321" s="2" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B1321" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C1321" s="5" t="n">
+        <v>710</v>
+      </c>
+      <c r="D1321" s="3" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="E1321" s="3" t="inlineStr">
+        <is>
+          <t>CIN25-006</t>
+        </is>
+      </c>
+      <c r="F1321" s="3" t="inlineStr">
+        <is>
+          <t>Delivery &amp; PIck Up Charge</t>
+        </is>
+      </c>
+      <c r="G1321" s="3" t="inlineStr">
+        <is>
+          <t>1100 · Trade Debtors</t>
+        </is>
+      </c>
+      <c r="H1321" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1322">
+      <c r="A1322" s="2" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B1322" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C1322" s="5" t="n">
+        <v>375</v>
+      </c>
+      <c r="D1322" s="3" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="E1322" s="3" t="inlineStr">
+        <is>
+          <t>CIN25-006</t>
+        </is>
+      </c>
+      <c r="F1322" s="3" t="inlineStr">
+        <is>
+          <t>Tear Down</t>
+        </is>
+      </c>
+      <c r="G1322" s="3" t="inlineStr">
+        <is>
+          <t>1100 · Trade Debtors</t>
+        </is>
+      </c>
+      <c r="H1322" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1323">
+      <c r="A1323" s="2" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B1323" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C1323" s="5" t="n">
+        <v>168.12</v>
+      </c>
+      <c r="D1323" s="3" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="E1323" s="3" t="inlineStr">
+        <is>
+          <t>CIN25-006</t>
+        </is>
+      </c>
+      <c r="F1323" s="3" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="G1323" s="3" t="inlineStr">
+        <is>
+          <t>1100 · Trade Debtors</t>
+        </is>
+      </c>
+      <c r="H1323" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1324">
+      <c r="A1324" s="2" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B1324" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C1324" s="5" t="n">
+        <v>561</v>
+      </c>
+      <c r="D1324" s="3" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="E1324" s="3" t="inlineStr">
+        <is>
+          <t>CIN25-006</t>
+        </is>
+      </c>
+      <c r="F1324" s="3" t="inlineStr">
+        <is>
+          <t>PV2412532S OFFICE TRAILER 8X24</t>
+        </is>
+      </c>
+      <c r="G1324" s="3" t="inlineStr">
+        <is>
+          <t>1100 · Trade Debtors</t>
+        </is>
+      </c>
+      <c r="H1324" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1325">
+      <c r="A1325" s="2" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B1325" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C1325" s="5" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="D1325" s="3" t="inlineStr">
+        <is>
+          <t>Invoice</t>
+        </is>
+      </c>
+      <c r="E1325" s="3" t="inlineStr">
+        <is>
+          <t>CIN25-006</t>
+        </is>
+      </c>
+      <c r="F1325" s="3" t="inlineStr">
+        <is>
+          <t>OFFICE TRAILER STEPS</t>
+        </is>
+      </c>
+      <c r="G1325" s="3" t="inlineStr">
+        <is>
+          <t>1100 · Trade Debtors</t>
+        </is>
+      </c>
+      <c r="H1325" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1326">
+      <c r="A1326" s="2" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B1326" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C1326" s="5" t="n">
         <v>48.95</v>
       </c>
-      <c r="D1265" s="3" t="inlineStr">
+      <c r="D1326" s="3" t="inlineStr">
         <is>
           <t>Invoice</t>
         </is>
       </c>
-      <c r="E1265" s="3" t="inlineStr">
+      <c r="E1326" s="3" t="inlineStr">
         <is>
           <t>CIN25-006</t>
         </is>
       </c>
-      <c r="F1265" s="3" t="inlineStr">
+      <c r="F1326" s="3" t="inlineStr">
         <is>
           <t>Tax</t>
         </is>
       </c>
-      <c r="G1265" s="3" t="inlineStr">
+      <c r="G1326" s="3" t="inlineStr">
         <is>
           <t>1100 · Trade Debtors</t>
         </is>
       </c>
-      <c r="H1265" s="4" t="n">
-        <v>400</v>
+      <c r="H1326" s="4" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="1327">
+      <c r="A1327" s="2" t="n">
+        <v>46053</v>
+      </c>
+      <c r="B1327" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C1327" s="5" t="n">
+        <v>304.75</v>
+      </c>
+      <c r="D1327" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1327" s="3" t="inlineStr">
+        <is>
+          <t>1501458748</t>
+        </is>
+      </c>
+      <c r="F1327" s="3" t="inlineStr">
+        <is>
+          <t>Const Restroom Lease</t>
+        </is>
+      </c>
+      <c r="G1327" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1327" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1328">
+      <c r="A1328" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B1328" s="3" t="inlineStr">
+        <is>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
+        </is>
+      </c>
+      <c r="C1328" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="D1328" s="3" t="inlineStr">
+        <is>
+          <t>General Journal</t>
+        </is>
+      </c>
+      <c r="E1328" s="3" t="inlineStr">
+        <is>
+          <t>16815</t>
+        </is>
+      </c>
+      <c r="F1328" s="3" t="inlineStr">
+        <is>
+          <t>Andy Remillard Per diem for week of 2/2/2026 - 2/8/2026</t>
+        </is>
+      </c>
+      <c r="G1328" s="3" t="inlineStr">
+        <is>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+        </is>
+      </c>
+      <c r="H1328" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1329">
+      <c r="A1329" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B1329" s="3" t="inlineStr">
+        <is>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
+        </is>
+      </c>
+      <c r="C1329" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="D1329" s="3" t="inlineStr">
+        <is>
+          <t>General Journal</t>
+        </is>
+      </c>
+      <c r="E1329" s="3" t="inlineStr">
+        <is>
+          <t>16815</t>
+        </is>
+      </c>
+      <c r="F1329" s="3" t="inlineStr">
+        <is>
+          <t>Mike Cogswell Per diem for week of 2/2/2026 - 2/8/2026</t>
+        </is>
+      </c>
+      <c r="G1329" s="3" t="inlineStr">
+        <is>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+        </is>
+      </c>
+      <c r="H1329" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1330">
+      <c r="A1330" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B1330" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1330" s="5" t="n">
+        <v>1561.25</v>
+      </c>
+      <c r="D1330" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1330" s="3" t="inlineStr">
+        <is>
+          <t>9791247316</t>
+        </is>
+      </c>
+      <c r="F1330" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PUMP,2 HP,3 PH,230/460V AC</t>
+        </is>
+      </c>
+      <c r="G1330" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1330" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1331">
+      <c r="A1331" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B1331" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1331" s="5" t="n">
+        <v>136.61</v>
+      </c>
+      <c r="D1331" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1331" s="3" t="inlineStr">
+        <is>
+          <t>9791247316</t>
+        </is>
+      </c>
+      <c r="F1331" s="3" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="G1331" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1331" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1332">
+      <c r="A1332" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B1332" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1332" s="5" t="n">
+        <v>196.92</v>
+      </c>
+      <c r="D1332" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1332" s="3" t="inlineStr">
+        <is>
+          <t>59116543</t>
+        </is>
+      </c>
+      <c r="F1332" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	316 Stainless Steel Check Valve with Fluoroelastomer Piston with Rubber Spring-Loaded Piston, 1...</t>
+        </is>
+      </c>
+      <c r="G1332" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1332" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1333">
+      <c r="A1333" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B1333" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1333" s="5" t="n">
+        <v>14.58</v>
+      </c>
+      <c r="D1333" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1333" s="3" t="inlineStr">
+        <is>
+          <t>59116543</t>
+        </is>
+      </c>
+      <c r="F1333" s="3" t="inlineStr">
+        <is>
+          <t>tax</t>
+        </is>
+      </c>
+      <c r="G1333" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1333" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1334">
+      <c r="A1334" s="2" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B1334" s="3" t="inlineStr">
+        <is>
+          <t>5121 · Freight &amp; Shipping (Direct)</t>
+        </is>
+      </c>
+      <c r="C1334" s="5" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="D1334" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1334" s="3" t="inlineStr">
+        <is>
+          <t>59116543</t>
+        </is>
+      </c>
+      <c r="F1334" s="3" t="inlineStr">
+        <is>
+          <t>Shipping</t>
+        </is>
+      </c>
+      <c r="G1334" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1334" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1335">
+      <c r="A1335" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B1335" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C1335" s="5" t="n">
+        <v>561</v>
+      </c>
+      <c r="D1335" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1335" s="3" t="inlineStr">
+        <is>
+          <t>256400488-003</t>
+        </is>
+      </c>
+      <c r="F1335" s="3" t="inlineStr">
+        <is>
+          <t>PV2412532S OFFICE TRAILER 8X24</t>
+        </is>
+      </c>
+      <c r="G1335" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1335" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1336">
+      <c r="A1336" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B1336" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C1336" s="5" t="n">
+        <v>66.5</v>
+      </c>
+      <c r="D1336" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1336" s="3" t="inlineStr">
+        <is>
+          <t>256400488-003</t>
+        </is>
+      </c>
+      <c r="F1336" s="3" t="inlineStr">
+        <is>
+          <t>OFFICE TRAILER STEPS</t>
+        </is>
+      </c>
+      <c r="G1336" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1336" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1337">
+      <c r="A1337" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B1337" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C1337" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1337" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1337" s="3" t="inlineStr">
+        <is>
+          <t>256400488-003</t>
+        </is>
+      </c>
+      <c r="F1337" s="3" t="inlineStr">
+        <is>
+          <t>BLOCK AND LEVEL + INSTALL OF 4 ANCHORS</t>
+        </is>
+      </c>
+      <c r="G1337" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1337" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1338">
+      <c r="A1338" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B1338" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C1338" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1338" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1338" s="3" t="inlineStr">
+        <is>
+          <t>256400488-003</t>
+        </is>
+      </c>
+      <c r="F1338" s="3" t="inlineStr">
+        <is>
+          <t>Delivery &amp; PIck Up Charge</t>
+        </is>
+      </c>
+      <c r="G1338" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1338" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1339">
+      <c r="A1339" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B1339" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C1339" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D1339" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1339" s="3" t="inlineStr">
+        <is>
+          <t>256400488-003</t>
+        </is>
+      </c>
+      <c r="F1339" s="3" t="inlineStr">
+        <is>
+          <t>Tear Down</t>
+        </is>
+      </c>
+      <c r="G1339" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1339" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1340">
+      <c r="A1340" s="2" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B1340" s="3" t="inlineStr">
+        <is>
+          <t>5115 · Rent - Equipment (direct)</t>
+        </is>
+      </c>
+      <c r="C1340" s="5" t="n">
+        <v>48.95</v>
+      </c>
+      <c r="D1340" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1340" s="3" t="inlineStr">
+        <is>
+          <t>256400488-003</t>
+        </is>
+      </c>
+      <c r="F1340" s="3" t="inlineStr">
+        <is>
+          <t>Tax</t>
+        </is>
+      </c>
+      <c r="G1340" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1340" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1341">
+      <c r="A1341" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B1341" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1341" s="5" t="n">
+        <v>20.91</v>
+      </c>
+      <c r="D1341" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1341" s="3" t="inlineStr">
+        <is>
+          <t>59278870</t>
+        </is>
+      </c>
+      <c r="F1341" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">	High-Pressure Brass Pipe Fitting, Through-Wall Straight Connector, 1/8 NPT Female</t>
+        </is>
+      </c>
+      <c r="G1341" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1341" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1342">
+      <c r="A1342" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B1342" s="3" t="inlineStr">
+        <is>
+          <t>5111 · Parts &amp; material costs (Direct)</t>
+        </is>
+      </c>
+      <c r="C1342" s="5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="D1342" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1342" s="3" t="inlineStr">
+        <is>
+          <t>59278870</t>
+        </is>
+      </c>
+      <c r="F1342" s="3" t="inlineStr">
+        <is>
+          <t>TAx</t>
+        </is>
+      </c>
+      <c r="G1342" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1342" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1343">
+      <c r="A1343" s="2" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B1343" s="3" t="inlineStr">
+        <is>
+          <t>5121 · Freight &amp; Shipping (Direct)</t>
+        </is>
+      </c>
+      <c r="C1343" s="5" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="D1343" s="3" t="inlineStr">
+        <is>
+          <t>Bill</t>
+        </is>
+      </c>
+      <c r="E1343" s="3" t="inlineStr">
+        <is>
+          <t>59278870</t>
+        </is>
+      </c>
+      <c r="F1343" s="3" t="inlineStr">
+        <is>
+          <t>Shipping</t>
+        </is>
+      </c>
+      <c r="G1343" s="3" t="inlineStr">
+        <is>
+          <t>2000 · Accounts Payable</t>
+        </is>
+      </c>
+      <c r="H1343" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1344">
+      <c r="A1344" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B1344" s="3" t="inlineStr">
+        <is>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
+        </is>
+      </c>
+      <c r="C1344" s="5" t="n">
+        <v>150</v>
+      </c>
+      <c r="D1344" s="3" t="inlineStr">
+        <is>
+          <t>General Journal</t>
+        </is>
+      </c>
+      <c r="E1344" s="3" t="inlineStr">
+        <is>
+          <t>16818</t>
+        </is>
+      </c>
+      <c r="F1344" s="3" t="inlineStr">
+        <is>
+          <t>Andy Remillard Per diem for week of 2/9/2026 - 2/15/2026</t>
+        </is>
+      </c>
+      <c r="G1344" s="3" t="inlineStr">
+        <is>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+        </is>
+      </c>
+      <c r="H1344" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1345">
+      <c r="A1345" s="2" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B1345" s="3" t="inlineStr">
+        <is>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
+        </is>
+      </c>
+      <c r="C1345" s="5" t="n">
+        <v>600</v>
+      </c>
+      <c r="D1345" s="3" t="inlineStr">
+        <is>
+          <t>General Journal</t>
+        </is>
+      </c>
+      <c r="E1345" s="3" t="inlineStr">
+        <is>
+          <t>16818</t>
+        </is>
+      </c>
+      <c r="F1345" s="3" t="inlineStr">
+        <is>
+          <t>Wyatt Staples Per diem for week of 2/4/2026 - 2/15/2026</t>
+        </is>
+      </c>
+      <c r="G1345" s="3" t="inlineStr">
+        <is>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+        </is>
+      </c>
+      <c r="H1345" s="4" t="n">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="1346">
+      <c r="A1346" s="2" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B1346" s="3" t="inlineStr">
+        <is>
+          <t>5108 · Meals &amp; entertainment (Direct)</t>
+        </is>
+      </c>
+      <c r="C1346" s="5" t="n">
+        <v>350</v>
+      </c>
+      <c r="D1346" s="3" t="inlineStr">
+        <is>
+          <t>General Journal</t>
+        </is>
+      </c>
+      <c r="E1346" s="3" t="inlineStr">
+        <is>
+          <t>16821</t>
+        </is>
+      </c>
+      <c r="F1346" s="3" t="inlineStr">
+        <is>
+          <t>Wyatt Staples Per diem for week of 2/16/2026 - 2/22/2026</t>
+        </is>
+      </c>
+      <c r="G1346" s="3" t="inlineStr">
+        <is>
+          <t>1006.2 · Calif B &amp; T Payroll Checking</t>
+        </is>
+      </c>
+      <c r="H1346" s="4" t="n">
+        <v>500</v>
       </c>
     </row>
   </sheetData>
@@ -47239,7 +50107,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>7080.14</v>
+        <v>8580.719999999999</v>
       </c>
     </row>
     <row r="7">
@@ -47299,7 +50167,7 @@
         </is>
       </c>
       <c r="C10" s="5" t="n">
-        <v>39079.07</v>
+        <v>41347.35</v>
       </c>
     </row>
     <row r="11">
@@ -47314,7 +50182,7 @@
         </is>
       </c>
       <c r="C11" s="5" t="n">
-        <v>152348.83</v>
+        <v>156831.42</v>
       </c>
     </row>
     <row r="12">
@@ -47344,7 +50212,7 @@
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>71061.59</v>
+        <v>74746.3</v>
       </c>
     </row>
     <row r="14">
@@ -47359,7 +50227,7 @@
         </is>
       </c>
       <c r="C14" s="5" t="n">
-        <v>151922.93</v>
+        <v>153903.09</v>
       </c>
     </row>
     <row r="15">
@@ -47374,7 +50242,7 @@
         </is>
       </c>
       <c r="C15" s="5" t="n">
-        <v>24920.47</v>
+        <v>25006.21</v>
       </c>
     </row>
     <row r="16">
@@ -47404,7 +50272,7 @@
         </is>
       </c>
       <c r="C17" s="5" t="n">
-        <v>9549.67</v>
+        <v>9839.120000000001</v>
       </c>
     </row>
     <row r="18">
